--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -374,6 +374,27 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1331-064</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REY S. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0887-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1334-066</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0000-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1333-303</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -10677,67 +10698,128 @@
       <x:c r="N6" s="7" t="s"/>
       <x:c r="O6" s="9" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
+      <x:c r="B7" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H7" s="12">
+        <x:v>46071.2285416667</x:v>
+      </x:c>
+      <x:c r="I7" s="13">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="n">
+        <x:v>1216143</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L7" s="12">
+        <x:v>46090.0772916667</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="21" t="s">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B8" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I8" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K8" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="21" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C9" s="22" t="s"/>
-      <x:c r="D9" s="22" t="s"/>
-      <x:c r="E9" s="23" t="s"/>
-      <x:c r="F9" s="23" t="s"/>
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="23" t="s"/>
+      <x:c r="F11" s="23" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="24" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="24" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C10" s="25" t="s"/>
-      <x:c r="D10" s="25" t="s"/>
-      <x:c r="E10" s="25" t="s"/>
-      <x:c r="F10" s="26" t="s">
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="28" t="s"/>
-      <x:c r="D11" s="28" t="s"/>
-      <x:c r="E11" s="28" t="s"/>
-      <x:c r="F11" s="29" t="n">
-        <x:v>1</x:v>
+      <x:c r="C13" s="28" t="s"/>
+      <x:c r="D13" s="28" t="s"/>
+      <x:c r="E13" s="28" t="s"/>
+      <x:c r="F13" s="29" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="30" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="30" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C12" s="31" t="s"/>
-      <x:c r="D12" s="31" t="s"/>
-      <x:c r="E12" s="31" t="s"/>
-      <x:c r="F12" s="32" t="n">
-        <x:v>1</x:v>
+      <x:c r="C14" s="31" t="s"/>
+      <x:c r="D14" s="31" t="s"/>
+      <x:c r="E14" s="31" t="s"/>
+      <x:c r="F14" s="32" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -11721,10 +11803,10 @@
   <x:mergeCells count="6">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -364,6 +364,18 @@
     <x:t>61-2-2026-1327-547</x:t>
   </x:si>
   <x:si>
+    <x:t>AL S. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk.Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0877-18(ren)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1340-327</x:t>
+  </x:si>
+  <x:si>
     <x:t>JUDELYN B. AMANIA</x:t>
   </x:si>
   <x:si>
@@ -376,12 +388,42 @@
     <x:t>61-2-2026-1331-064</x:t>
   </x:si>
   <x:si>
+    <x:t>REMEGIO T. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a Prk.Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0879-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1344-597</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0880-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1343-619</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REMEGIO T. BURBURAN JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a Prk.daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0881-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1342-435</x:t>
+  </x:si>
+  <x:si>
     <x:t>REY S. BURBURAN</x:t>
   </x:si>
   <x:si>
-    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
     <x:t>MS9/FV-0887-18</x:t>
   </x:si>
   <x:si>
@@ -395,6 +437,51 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1333-303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCHER C COTINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a N/A, Sto. Nino, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1347-156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLAUDIO  E. ELNAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a N/A, Poblacion, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1348-671</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDWIN M SAGAYNO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-SROPIX-16152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1349-935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAMON M SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-SROPIX-16133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1350-437</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -10678,19 +10765,19 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46072.0333449074</x:v>
       </x:c>
       <x:c r="I6" s="13">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216156</x:v>
       </x:c>
       <x:c r="K6" s="14" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46090.2584837963</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>19</x:v>
@@ -10719,19 +10806,19 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I7" s="13">
-        <x:v>46058</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K7" s="14" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
         <x:v>19</x:v>
@@ -10743,92 +10830,398 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>115</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D8" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E8" s="15" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F8" s="15" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G8" s="15" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I8" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J8" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K8" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L8" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="23" t="s"/>
-      <x:c r="F11" s="23" t="s"/>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46072.0792939815</x:v>
+      </x:c>
+      <x:c r="I9" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="n">
+        <x:v>1216150</x:v>
+      </x:c>
+      <x:c r="K9" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L9" s="20">
+        <x:v>46090.220787037</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="s">
-        <x:v>33</x:v>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46072.0497337963</x:v>
+      </x:c>
+      <x:c r="I10" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>1216148</x:v>
+      </x:c>
+      <x:c r="K10" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="20">
+        <x:v>46090.2102430556</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="28" t="s"/>
-      <x:c r="F13" s="29" t="n">
-        <x:v>3</x:v>
+      <x:c r="C11" s="15" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46071.2285416667</x:v>
+      </x:c>
+      <x:c r="I11" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1216143</x:v>
+      </x:c>
+      <x:c r="K11" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L11" s="20">
+        <x:v>46090.0772916667</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="s"/>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="31" t="s"/>
-      <x:c r="F14" s="32" t="n">
-        <x:v>3</x:v>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L12" s="20">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46073.0262847222</x:v>
+      </x:c>
+      <x:c r="I13" s="18">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1216157</x:v>
+      </x:c>
+      <x:c r="K13" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L13" s="20">
+        <x:v>46090.267025463</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46073.0478472222</x:v>
+      </x:c>
+      <x:c r="I14" s="18">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1216153</x:v>
+      </x:c>
+      <x:c r="K14" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L14" s="20">
+        <x:v>46090.2431828704</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46073.061099537</x:v>
+      </x:c>
+      <x:c r="I15" s="18">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
+        <x:v>1216151</x:v>
+      </x:c>
+      <x:c r="K15" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L15" s="20">
+        <x:v>46090.2266435185</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I16" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K16" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L16" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="21" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="23" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="29" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="27" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C22" s="28" t="s"/>
+      <x:c r="D22" s="28" t="s"/>
+      <x:c r="E22" s="28" t="s"/>
+      <x:c r="F22" s="29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="30" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C23" s="31" t="s"/>
+      <x:c r="D23" s="31" t="s"/>
+      <x:c r="E23" s="31" t="s"/>
+      <x:c r="F23" s="32" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
@@ -11800,13 +12193,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="7">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B19:F19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -362,6 +362,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1327-547</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTURO D ANTONIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, San Carlos, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17-SROPIX-11057</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1346-185</x:t>
   </x:si>
   <x:si>
     <x:t>AL S. BURBURAN</x:t>
@@ -10747,7 +10759,7 @@
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
         <x:v>111</x:v>
@@ -10765,19 +10777,19 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46072.0333449074</x:v>
+        <x:v>46072.3153009259</x:v>
       </x:c>
       <x:c r="I6" s="13">
-        <x:v>46058</x:v>
+        <x:v>46114</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1216156</x:v>
+        <x:v>1216162</x:v>
       </x:c>
       <x:c r="K6" s="14" t="n">
-        <x:v>1830</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46090.2584837963</x:v>
+        <x:v>46090.311412037</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>19</x:v>
@@ -10806,19 +10818,19 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46072.0333449074</x:v>
       </x:c>
       <x:c r="I7" s="13">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216156</x:v>
       </x:c>
       <x:c r="K7" s="14" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46090.2584837963</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
         <x:v>19</x:v>
@@ -10845,19 +10857,19 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I8" s="18">
-        <x:v>46058</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J8" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K8" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L8" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>19</x:v>
@@ -10868,34 +10880,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>119</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D9" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="15" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F9" s="15" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G9" s="15" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I9" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J9" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K9" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L9" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>19</x:v>
@@ -10906,7 +10918,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D10" s="16" t="s">
         <x:v>15</x:v>
@@ -10921,19 +10933,19 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I10" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J10" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K10" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L10" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>19</x:v>
@@ -10950,28 +10962,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="15" t="s">
-        <x:v>123</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F11" s="15" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G11" s="15" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H11" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I11" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J11" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K11" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>19</x:v>
@@ -10982,34 +10994,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C12" s="15" t="s">
-        <x:v>130</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D12" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="15" t="s">
-        <x:v>133</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F12" s="15" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G12" s="15" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I12" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>19</x:v>
@@ -11017,10 +11029,10 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D13" s="16" t="s">
         <x:v>15</x:v>
@@ -11035,19 +11047,19 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46071.2072569444</x:v>
       </x:c>
       <x:c r="I13" s="18">
-        <x:v>46042</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216142</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46090.0616666667</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>19</x:v>
@@ -11073,19 +11085,19 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I14" s="18">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>19</x:v>
@@ -11111,19 +11123,19 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>46036</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>19</x:v>
@@ -11140,90 +11152,137 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="15" t="s">
-        <x:v>145</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F16" s="15" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G16" s="15" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>45824</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I17" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K17" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L17" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="21" t="s">
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="21" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="23" t="s"/>
+      <x:c r="C20" s="22" t="s"/>
+      <x:c r="D20" s="22" t="s"/>
+      <x:c r="E20" s="23" t="s"/>
+      <x:c r="F20" s="23" t="s"/>
     </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="24" t="s">
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="24" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C20" s="25" t="s"/>
-      <x:c r="D20" s="25" t="s"/>
-      <x:c r="E20" s="25" t="s"/>
-      <x:c r="F20" s="26" t="s">
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="25" t="s"/>
+      <x:c r="F21" s="26" t="s">
         <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="29" t="n">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="27" t="s">
-        <x:v>27</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C22" s="28" t="s"/>
       <x:c r="D22" s="28" t="s"/>
       <x:c r="E22" s="28" t="s"/>
       <x:c r="F22" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C23" s="28" t="s"/>
+      <x:c r="D23" s="28" t="s"/>
+      <x:c r="E23" s="28" t="s"/>
+      <x:c r="F23" s="29" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="27" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C24" s="28" t="s"/>
+      <x:c r="D24" s="28" t="s"/>
+      <x:c r="E24" s="28" t="s"/>
+      <x:c r="F24" s="29" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="30" t="s">
+    <x:row r="25" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B25" s="30" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C23" s="31" t="s"/>
-      <x:c r="D23" s="31" t="s"/>
-      <x:c r="E23" s="31" t="s"/>
-      <x:c r="F23" s="32" t="n">
-        <x:v>11</x:v>
+      <x:c r="C25" s="31" t="s"/>
+      <x:c r="D25" s="31" t="s"/>
+      <x:c r="E25" s="31" t="s"/>
+      <x:c r="F25" s="32" t="n">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
@@ -12193,14 +12252,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -388,6 +388,18 @@
     <x:t>61-2-2026-1340-327</x:t>
   </x:si>
   <x:si>
+    <x:t>FEY S. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0886-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1332-813</x:t>
+  </x:si>
+  <x:si>
     <x:t>JUDELYN B. AMANIA</x:t>
   </x:si>
   <x:si>
@@ -475,10 +487,19 @@
     <x:t>61-2-2026-1348-671</x:t>
   </x:si>
   <x:si>
+    <x:t>EDGAR S SERENCIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24-SROPIX-16132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1351-693</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDWIN M SAGAYNO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
     <x:t>-SROPIX-16152</x:t>
@@ -10857,19 +10878,19 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46071.1677662037</x:v>
       </x:c>
       <x:c r="I8" s="18">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J8" s="16" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216165</x:v>
       </x:c>
       <x:c r="K8" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L8" s="20">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46091.1948842593</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>19</x:v>
@@ -10895,19 +10916,19 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I9" s="18">
-        <x:v>46058</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J9" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K9" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L9" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>19</x:v>
@@ -10918,34 +10939,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>123</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D10" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E10" s="15" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F10" s="15" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G10" s="15" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I10" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J10" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K10" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L10" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>19</x:v>
@@ -10956,7 +10977,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D11" s="16" t="s">
         <x:v>15</x:v>
@@ -10971,19 +10992,19 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="H11" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I11" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J11" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K11" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>19</x:v>
@@ -11000,28 +11021,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="15" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F12" s="15" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G12" s="15" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I12" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>19</x:v>
@@ -11032,34 +11053,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>134</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D13" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="15" t="s">
-        <x:v>137</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F13" s="15" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G13" s="15" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I13" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>19</x:v>
@@ -11067,10 +11088,10 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="15" t="s">
-        <x:v>140</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D14" s="16" t="s">
         <x:v>15</x:v>
@@ -11085,19 +11106,19 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46071.2072569444</x:v>
       </x:c>
       <x:c r="I14" s="18">
-        <x:v>46042</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216142</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46090.0616666667</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>19</x:v>
@@ -11123,19 +11144,19 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I15" s="18">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>19</x:v>
@@ -11161,19 +11182,19 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>46036</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>19</x:v>
@@ -11190,101 +11211,175 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E17" s="15" t="s">
-        <x:v>149</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F17" s="15" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G17" s="15" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46073.1095023148</x:v>
       </x:c>
       <x:c r="I17" s="18">
         <x:v>45824</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216164</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46091.121087963</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="21" t="s">
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46073.061099537</x:v>
+      </x:c>
+      <x:c r="I18" s="18">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="n">
+        <x:v>1216151</x:v>
+      </x:c>
+      <x:c r="K18" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L18" s="20">
+        <x:v>46090.2266435185</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I19" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L19" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="21" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C20" s="22" t="s"/>
-      <x:c r="D20" s="22" t="s"/>
-      <x:c r="E20" s="23" t="s"/>
-      <x:c r="F20" s="23" t="s"/>
+      <x:c r="C22" s="22" t="s"/>
+      <x:c r="D22" s="22" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="23" t="s"/>
     </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="24" t="s">
+    <x:row r="23" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B23" s="24" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C21" s="25" t="s"/>
-      <x:c r="D21" s="25" t="s"/>
-      <x:c r="E21" s="25" t="s"/>
-      <x:c r="F21" s="26" t="s">
+      <x:c r="C23" s="25" t="s"/>
+      <x:c r="D23" s="25" t="s"/>
+      <x:c r="E23" s="25" t="s"/>
+      <x:c r="F23" s="26" t="s">
         <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="27" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C22" s="28" t="s"/>
-      <x:c r="D22" s="28" t="s"/>
-      <x:c r="E22" s="28" t="s"/>
-      <x:c r="F22" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C23" s="28" t="s"/>
-      <x:c r="D23" s="28" t="s"/>
-      <x:c r="E23" s="28" t="s"/>
-      <x:c r="F23" s="29" t="n">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="27" t="s">
-        <x:v>27</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C24" s="28" t="s"/>
       <x:c r="D24" s="28" t="s"/>
       <x:c r="E24" s="28" t="s"/>
       <x:c r="F24" s="29" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="30" t="s">
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C25" s="28" t="s"/>
+      <x:c r="D25" s="28" t="s"/>
+      <x:c r="E25" s="28" t="s"/>
+      <x:c r="F25" s="29" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="27" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C26" s="28" t="s"/>
+      <x:c r="D26" s="28" t="s"/>
+      <x:c r="E26" s="28" t="s"/>
+      <x:c r="F26" s="29" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="30" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C25" s="31" t="s"/>
-      <x:c r="D25" s="31" t="s"/>
-      <x:c r="E25" s="31" t="s"/>
-      <x:c r="F25" s="32" t="n">
-        <x:v>12</x:v>
+      <x:c r="C27" s="31" t="s"/>
+      <x:c r="D27" s="31" t="s"/>
+      <x:c r="E27" s="31" t="s"/>
+      <x:c r="F27" s="32" t="n">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -12255,12 +12350,12 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B20:F20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B22:F22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -461,6 +461,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1333-303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RHEINT JAY CENO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zone 9, tiguma, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1281-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1372-847</x:t>
   </x:si>
   <x:si>
     <x:t>ARCHER C COTINA</x:t>
@@ -11126,7 +11138,7 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="15" t="s">
         <x:v>144</x:v>
@@ -11144,19 +11156,19 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46079.0151851852</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>46042</x:v>
+        <x:v>45602</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216174</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>3990</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46093.1514351852</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>19</x:v>
@@ -11182,19 +11194,19 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I16" s="18">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>19</x:v>
@@ -11220,19 +11232,19 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>46073.1095023148</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I17" s="18">
-        <x:v>45824</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1216164</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46091.121087963</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>19</x:v>
@@ -11249,28 +11261,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="15" t="s">
-        <x:v>153</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F18" s="15" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G18" s="15" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.1095023148</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>46036</x:v>
+        <x:v>45824</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216164</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46091.121087963</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>19</x:v>
@@ -11281,106 +11293,143 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C19" s="15" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D19" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="15" t="s">
-        <x:v>153</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F19" s="15" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G19" s="15" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H19" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>45824</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J19" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M19" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I20" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L20" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="21" t="s">
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="21" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C22" s="22" t="s"/>
-      <x:c r="D22" s="22" t="s"/>
-      <x:c r="E22" s="23" t="s"/>
-      <x:c r="F22" s="23" t="s"/>
+      <x:c r="C23" s="22" t="s"/>
+      <x:c r="D23" s="22" t="s"/>
+      <x:c r="E23" s="23" t="s"/>
+      <x:c r="F23" s="23" t="s"/>
     </x:row>
-    <x:row r="23" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B23" s="24" t="s">
+    <x:row r="24" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B24" s="24" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C23" s="25" t="s"/>
-      <x:c r="D23" s="25" t="s"/>
-      <x:c r="E23" s="25" t="s"/>
-      <x:c r="F23" s="26" t="s">
+      <x:c r="C24" s="25" t="s"/>
+      <x:c r="D24" s="25" t="s"/>
+      <x:c r="E24" s="25" t="s"/>
+      <x:c r="F24" s="26" t="s">
         <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="27" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C24" s="28" t="s"/>
-      <x:c r="D24" s="28" t="s"/>
-      <x:c r="E24" s="28" t="s"/>
-      <x:c r="F24" s="29" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C25" s="28" t="s"/>
       <x:c r="D25" s="28" t="s"/>
       <x:c r="E25" s="28" t="s"/>
       <x:c r="F25" s="29" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
       <x:c r="B26" s="27" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C26" s="28" t="s"/>
       <x:c r="D26" s="28" t="s"/>
       <x:c r="E26" s="28" t="s"/>
       <x:c r="F26" s="29" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="27" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C27" s="28" t="s"/>
+      <x:c r="D27" s="28" t="s"/>
+      <x:c r="E27" s="28" t="s"/>
+      <x:c r="F27" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="30" t="s">
+    <x:row r="28" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B28" s="30" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C27" s="31" t="s"/>
-      <x:c r="D27" s="31" t="s"/>
-      <x:c r="E27" s="31" t="s"/>
-      <x:c r="F27" s="32" t="n">
-        <x:v>14</x:v>
+      <x:c r="C28" s="31" t="s"/>
+      <x:c r="D28" s="31" t="s"/>
+      <x:c r="E28" s="31" t="s"/>
+      <x:c r="F28" s="32" t="n">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
@@ -12350,12 +12399,12 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B22:F22"/>
-    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B23:F23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -487,7 +487,7 @@
     <x:t>61-2-2026-1347-156</x:t>
   </x:si>
   <x:si>
-    <x:t>CLAUDIO  E. ELNAR</x:t>
+    <x:t>CLAUDIO E. ELNAR</x:t>
   </x:si>
   <x:si>
     <x:t>N/a N/A, Poblacion, Tukuran, Zamboanga Del Sur</x:t>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -412,6 +412,18 @@
     <x:t>61-2-2026-1331-064</x:t>
   </x:si>
   <x:si>
+    <x:t>NDC FISHING CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRK. KAMANGGAHAN, CURVADA, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1006-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1337-307</x:t>
+  </x:si>
+  <x:si>
     <x:t>REMEGIO T. BURBURAN</x:t>
   </x:si>
   <x:si>
@@ -527,6 +539,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1350-437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODEL PALMERO TOLENTINO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok 4, GUIPOS, Guipos, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17SROPIX11062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1336-018</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -10966,19 +10990,19 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46071.3305671296</x:v>
       </x:c>
       <x:c r="I10" s="18">
-        <x:v>46058</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J10" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216193</x:v>
       </x:c>
       <x:c r="K10" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L10" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46094.1906365741</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>19</x:v>
@@ -10989,34 +11013,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
-        <x:v>127</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D11" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="15" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F11" s="15" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G11" s="15" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H11" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I11" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J11" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K11" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>19</x:v>
@@ -11027,7 +11051,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C12" s="15" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D12" s="16" t="s">
         <x:v>15</x:v>
@@ -11042,19 +11066,19 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I12" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>19</x:v>
@@ -11071,28 +11095,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="15" t="s">
-        <x:v>131</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F13" s="15" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G13" s="15" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I13" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>19</x:v>
@@ -11103,34 +11127,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="15" t="s">
-        <x:v>138</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D14" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="15" t="s">
-        <x:v>141</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F14" s="15" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G14" s="15" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I14" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>19</x:v>
@@ -11141,7 +11165,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="15" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D15" s="16" t="s">
         <x:v>15</x:v>
@@ -11156,19 +11180,19 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46079.0151851852</x:v>
+        <x:v>46071.2072569444</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>45602</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216174</x:v>
+        <x:v>1216142</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
-        <x:v>3990</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46093.1514351852</x:v>
+        <x:v>46090.0616666667</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>19</x:v>
@@ -11176,7 +11200,7 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="15" t="s">
         <x:v>148</x:v>
@@ -11194,19 +11218,19 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46079.0151851852</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>46042</x:v>
+        <x:v>45602</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216174</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>3990</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46093.1514351852</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>19</x:v>
@@ -11232,19 +11256,19 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I17" s="18">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>19</x:v>
@@ -11270,19 +11294,19 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46073.1095023148</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>45824</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216164</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46091.121087963</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>19</x:v>
@@ -11299,28 +11323,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="15" t="s">
-        <x:v>157</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="F19" s="15" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G19" s="15" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H19" s="17">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.1095023148</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>46036</x:v>
+        <x:v>45824</x:v>
       </x:c>
       <x:c r="J19" s="16" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216164</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46091.121087963</x:v>
       </x:c>
       <x:c r="M19" s="15" t="s">
         <x:v>19</x:v>
@@ -11331,107 +11355,181 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C20" s="15" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D20" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="15" t="s">
-        <x:v>157</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="F20" s="15" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G20" s="15" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H20" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I20" s="18">
-        <x:v>45824</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J20" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K20" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L20" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M20" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="21" t="s">
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I21" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L21" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46071.2853587963</x:v>
+      </x:c>
+      <x:c r="I22" s="18">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="n">
+        <x:v>1216191</x:v>
+      </x:c>
+      <x:c r="K22" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L22" s="20">
+        <x:v>46094.1777199074</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="21" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C23" s="22" t="s"/>
-      <x:c r="D23" s="22" t="s"/>
-      <x:c r="E23" s="23" t="s"/>
-      <x:c r="F23" s="23" t="s"/>
+      <x:c r="C25" s="22" t="s"/>
+      <x:c r="D25" s="22" t="s"/>
+      <x:c r="E25" s="23" t="s"/>
+      <x:c r="F25" s="23" t="s"/>
     </x:row>
-    <x:row r="24" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B24" s="24" t="s">
+    <x:row r="26" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B26" s="24" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C24" s="25" t="s"/>
-      <x:c r="D24" s="25" t="s"/>
-      <x:c r="E24" s="25" t="s"/>
-      <x:c r="F24" s="26" t="s">
+      <x:c r="C26" s="25" t="s"/>
+      <x:c r="D26" s="25" t="s"/>
+      <x:c r="E26" s="25" t="s"/>
+      <x:c r="F26" s="26" t="s">
         <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="27" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C25" s="28" t="s"/>
-      <x:c r="D25" s="28" t="s"/>
-      <x:c r="E25" s="28" t="s"/>
-      <x:c r="F25" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C26" s="28" t="s"/>
-      <x:c r="D26" s="28" t="s"/>
-      <x:c r="E26" s="28" t="s"/>
-      <x:c r="F26" s="29" t="n">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
       <x:c r="B27" s="27" t="s">
-        <x:v>27</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C27" s="28" t="s"/>
       <x:c r="D27" s="28" t="s"/>
       <x:c r="E27" s="28" t="s"/>
       <x:c r="F27" s="29" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B28" s="30" t="s">
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C28" s="28" t="s"/>
+      <x:c r="D28" s="28" t="s"/>
+      <x:c r="E28" s="28" t="s"/>
+      <x:c r="F28" s="29" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="27" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C29" s="28" t="s"/>
+      <x:c r="D29" s="28" t="s"/>
+      <x:c r="E29" s="28" t="s"/>
+      <x:c r="F29" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B30" s="30" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C28" s="31" t="s"/>
-      <x:c r="D28" s="31" t="s"/>
-      <x:c r="E28" s="31" t="s"/>
-      <x:c r="F28" s="32" t="n">
-        <x:v>15</x:v>
+      <x:c r="C30" s="31" t="s"/>
+      <x:c r="D30" s="31" t="s"/>
+      <x:c r="E30" s="31" t="s"/>
+      <x:c r="F30" s="32" t="n">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
@@ -12399,12 +12497,12 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B23:F23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B25:F25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -172,16 +172,16 @@
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
+    <x:t>MP-ROIX-01008-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-8-2025-1095</x:t>
+  </x:si>
+  <x:si>
     <x:t>MP-ROIX-01007-25</x:t>
   </x:si>
   <x:si>
     <x:t>61-8-2025-1093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MP-ROIX-01008-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-8-2025-1095</x:t>
   </x:si>
   <x:si>
     <x:t>LORNA Y. BALONGCAS</x:t>
@@ -2880,19 +2880,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>45875.2324652778</x:v>
+        <x:v>45875.361724537</x:v>
       </x:c>
       <x:c r="I8" s="18">
-        <x:v>45903</x:v>
+        <x:v>45921</x:v>
       </x:c>
       <x:c r="J8" s="16" t="n">
-        <x:v>1215852</x:v>
+        <x:v>1215851</x:v>
       </x:c>
       <x:c r="K8" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L8" s="20">
-        <x:v>45876.2319791667</x:v>
+        <x:v>45876.2230902778</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>19</x:v>
@@ -2918,19 +2918,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>45875.361724537</x:v>
+        <x:v>45875.2324652778</x:v>
       </x:c>
       <x:c r="I9" s="18">
-        <x:v>45921</x:v>
+        <x:v>45903</x:v>
       </x:c>
       <x:c r="J9" s="16" t="n">
-        <x:v>1215851</x:v>
+        <x:v>1215852</x:v>
       </x:c>
       <x:c r="K9" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L9" s="20">
-        <x:v>45876.2230902778</x:v>
+        <x:v>45876.2319791667</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>19</x:v>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -16,58 +16,22 @@
     <x:sheet name="March 2026" sheetId="14" r:id="rId14"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Ship Station License DOMESTIC Trade (RENEWAL)</x:t>
@@ -560,7 +524,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -587,12 +551,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -600,6 +558,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -617,13 +596,6 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
@@ -637,6 +609,14 @@
       <x:sz val="14"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -662,8 +642,19 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="17">
     <x:border/>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
     <x:border>
       <x:left style="thin">
         <x:color rgb="FF000000"/>
@@ -679,17 +670,6 @@
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -870,8 +850,59 @@
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thick">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thick">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -882,79 +913,103 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="14" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="15" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="16" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
@@ -962,113 +1017,142 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1332,302 +1416,278 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
+      <x:c r="E6" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="s">
+      <x:c r="F6" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="s">
+      <x:c r="G6" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="H6" s="13">
+        <x:v>45862.256875</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45908</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215838</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45862.3066319444</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
+      <x:c r="F7" s="17" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K5" s="10" t="s">
+      <x:c r="G7" s="17" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L5" s="10" t="s">
+      <x:c r="H7" s="18">
+        <x:v>45861.1595717593</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1215833</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45862.1034606481</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
+      <x:c r="D8" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
+      <x:c r="F8" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="G8" s="21" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
+      <x:c r="H8" s="22">
+        <x:v>45861.1361574074</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1215836</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>7950</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>45862.1391203704</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="C9" s="21" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F9" s="21" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="G9" s="21" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45862.256875</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45908</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215838</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45862.3066319444</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45861.1595717593</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1215833</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45862.1034606481</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
-        <x:v>45861.1361574074</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
+      <x:c r="H9" s="22">
+        <x:v>45861.181087963</x:v>
+      </x:c>
+      <x:c r="I9" s="23">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1215836</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
-        <x:v>7950</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>45862.1391203704</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
-        <x:v>45861.181087963</x:v>
-      </x:c>
-      <x:c r="I9" s="18">
-        <x:v>46273</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="n">
+      <x:c r="J9" s="21" t="n">
         <x:v>1215835</x:v>
       </x:c>
-      <x:c r="K9" s="19" t="n">
+      <x:c r="K9" s="24" t="n">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L9" s="22">
         <x:v>45862.1344560185</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="21" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
+      <x:c r="B12" s="25" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C12" s="26" t="s"/>
+      <x:c r="D12" s="26" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="27" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
-        <x:v>33</x:v>
+      <x:c r="B13" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s"/>
+      <x:c r="D13" s="29" t="s"/>
+      <x:c r="E13" s="29" t="s"/>
+      <x:c r="F13" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="32" t="s"/>
+      <x:c r="D14" s="32" t="s"/>
+      <x:c r="E14" s="32" t="s"/>
+      <x:c r="F14" s="33" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="31" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="32" t="s"/>
+      <x:c r="D15" s="32" t="s"/>
+      <x:c r="E15" s="32" t="s"/>
+      <x:c r="F15" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="34" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C16" s="35" t="s"/>
+      <x:c r="D16" s="35" t="s"/>
+      <x:c r="E16" s="35" t="s"/>
+      <x:c r="F16" s="36" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -2692,411 +2752,387 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45866.2802893519</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>45866.2803009259</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215849</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45873.1184143519</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>45875.2238888889</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1215853</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>4030</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45876.2432986111</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>45875.361724537</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1215851</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>45876.2230902778</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F9" s="21" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G9" s="21" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H9" s="22">
+        <x:v>45875.2324652778</x:v>
+      </x:c>
+      <x:c r="I9" s="23">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="n">
+        <x:v>1215852</x:v>
+      </x:c>
+      <x:c r="K9" s="24" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="22">
+        <x:v>45876.2319791667</x:v>
+      </x:c>
+      <x:c r="M9" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E10" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>45879.4885069444</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1215863</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>45884.277650463</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45866.2802893519</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>45866.2803009259</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215849</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45873.1184143519</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="C11" s="11" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="D11" s="12" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45875.2238888889</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1215853</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>4030</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45876.2432986111</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
+      <x:c r="F11" s="11" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="G11" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
-        <x:v>45875.361724537</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1215851</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>45876.2230902778</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
-        <x:v>45875.2324652778</x:v>
-      </x:c>
-      <x:c r="I9" s="18">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="n">
-        <x:v>1215852</x:v>
-      </x:c>
-      <x:c r="K9" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>45876.2319791667</x:v>
-      </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45879.4885069444</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1215863</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>1650</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
-        <x:v>45884.277650463</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="13">
         <x:v>45887.5499305556</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="13">
         <x:v>45887.5499537037</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="12" t="n">
         <x:v>1215865</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="15" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="16">
         <x:v>45891.1027199074</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="23" t="s"/>
+      <x:c r="B14" s="25" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="27" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="s">
-        <x:v>33</x:v>
+      <x:c r="B15" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C15" s="29" t="s"/>
+      <x:c r="D15" s="29" t="s"/>
+      <x:c r="E15" s="29" t="s"/>
+      <x:c r="F15" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="B16" s="31" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C16" s="32" t="s"/>
+      <x:c r="D16" s="32" t="s"/>
+      <x:c r="E16" s="32" t="s"/>
+      <x:c r="F16" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="B17" s="31" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C17" s="32" t="s"/>
+      <x:c r="D17" s="32" t="s"/>
+      <x:c r="E17" s="32" t="s"/>
+      <x:c r="F17" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="27" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
+      <x:c r="B18" s="31" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C18" s="32" t="s"/>
+      <x:c r="D18" s="32" t="s"/>
+      <x:c r="E18" s="32" t="s"/>
+      <x:c r="F18" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="n">
+      <x:c r="B19" s="31" t="s">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="s"/>
+      <x:c r="D19" s="32" t="s"/>
+      <x:c r="E19" s="32" t="s"/>
+      <x:c r="F19" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="27" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C20" s="28" t="s"/>
-      <x:c r="D20" s="28" t="s"/>
-      <x:c r="E20" s="28" t="s"/>
-      <x:c r="F20" s="29" t="n">
+      <x:c r="B20" s="31" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C20" s="32" t="s"/>
+      <x:c r="D20" s="32" t="s"/>
+      <x:c r="E20" s="32" t="s"/>
+      <x:c r="F20" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C21" s="31" t="s"/>
-      <x:c r="D21" s="31" t="s"/>
-      <x:c r="E21" s="31" t="s"/>
-      <x:c r="F21" s="32" t="n">
+      <x:c r="B21" s="34" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C21" s="35" t="s"/>
+      <x:c r="D21" s="35" t="s"/>
+      <x:c r="E21" s="35" t="s"/>
+      <x:c r="F21" s="36" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4159,190 +4195,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45887.2917592593</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215880</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45903.1177546296</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="37" t="s"/>
+      <x:c r="C7" s="37" t="s"/>
+      <x:c r="D7" s="37" t="s"/>
+      <x:c r="E7" s="37" t="s"/>
+      <x:c r="F7" s="37" t="s"/>
+      <x:c r="G7" s="37" t="s"/>
+      <x:c r="H7" s="37" t="s"/>
+      <x:c r="I7" s="37" t="s"/>
+      <x:c r="J7" s="37" t="s"/>
+      <x:c r="K7" s="37" t="s"/>
+      <x:c r="L7" s="37" t="s"/>
+      <x:c r="M7" s="37" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="38" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C9" s="39" t="s"/>
+      <x:c r="D9" s="39" t="s"/>
+      <x:c r="E9" s="40" t="s"/>
+      <x:c r="F9" s="40" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B10" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s"/>
+      <x:c r="D10" s="29" t="s"/>
+      <x:c r="E10" s="29" t="s"/>
+      <x:c r="F10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B11" s="31" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C11" s="32" t="s"/>
+      <x:c r="D11" s="32" t="s"/>
+      <x:c r="E11" s="32" t="s"/>
+      <x:c r="F11" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45887.2917592593</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215880</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45903.1177546296</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C9" s="22" t="s"/>
-      <x:c r="D9" s="22" t="s"/>
-      <x:c r="E9" s="23" t="s"/>
-      <x:c r="F9" s="23" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="24" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C10" s="25" t="s"/>
-      <x:c r="D10" s="25" t="s"/>
-      <x:c r="E10" s="25" t="s"/>
-      <x:c r="F10" s="26" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="27" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s"/>
-      <x:c r="D11" s="28" t="s"/>
-      <x:c r="E11" s="28" t="s"/>
-      <x:c r="F11" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" s="31" t="s"/>
-      <x:c r="D12" s="31" t="s"/>
-      <x:c r="E12" s="31" t="s"/>
-      <x:c r="F12" s="32" t="n">
+      <x:c r="B12" s="34" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="35" t="s"/>
+      <x:c r="D12" s="35" t="s"/>
+      <x:c r="E12" s="35" t="s"/>
+      <x:c r="F12" s="36" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -5410,190 +5442,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45962</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45944.1129282407</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215998</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45971.316400463</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="37" t="s"/>
+      <x:c r="C7" s="37" t="s"/>
+      <x:c r="D7" s="37" t="s"/>
+      <x:c r="E7" s="37" t="s"/>
+      <x:c r="F7" s="37" t="s"/>
+      <x:c r="G7" s="37" t="s"/>
+      <x:c r="H7" s="37" t="s"/>
+      <x:c r="I7" s="37" t="s"/>
+      <x:c r="J7" s="37" t="s"/>
+      <x:c r="K7" s="37" t="s"/>
+      <x:c r="L7" s="37" t="s"/>
+      <x:c r="M7" s="37" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="38" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C9" s="39" t="s"/>
+      <x:c r="D9" s="39" t="s"/>
+      <x:c r="E9" s="40" t="s"/>
+      <x:c r="F9" s="40" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B10" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s"/>
+      <x:c r="D10" s="29" t="s"/>
+      <x:c r="E10" s="29" t="s"/>
+      <x:c r="F10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B11" s="31" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C11" s="32" t="s"/>
+      <x:c r="D11" s="32" t="s"/>
+      <x:c r="E11" s="32" t="s"/>
+      <x:c r="F11" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45944.1129282407</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215998</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45971.316400463</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C9" s="22" t="s"/>
-      <x:c r="D9" s="22" t="s"/>
-      <x:c r="E9" s="23" t="s"/>
-      <x:c r="F9" s="23" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="24" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C10" s="25" t="s"/>
-      <x:c r="D10" s="25" t="s"/>
-      <x:c r="E10" s="25" t="s"/>
-      <x:c r="F10" s="26" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="27" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s"/>
-      <x:c r="D11" s="28" t="s"/>
-      <x:c r="E11" s="28" t="s"/>
-      <x:c r="F11" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" s="31" t="s"/>
-      <x:c r="D12" s="31" t="s"/>
-      <x:c r="E12" s="31" t="s"/>
-      <x:c r="F12" s="32" t="n">
+      <x:c r="B12" s="34" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="35" t="s"/>
+      <x:c r="D12" s="35" t="s"/>
+      <x:c r="E12" s="35" t="s"/>
+      <x:c r="F12" s="36" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -6661,226 +6689,228 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46000.4750694444</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216048</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46013.2950462963</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C7" s="17" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E7" s="17" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>46000.180775463</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1216037</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46006.2645138889</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46000.4750694444</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45992</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216048</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>744</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46013.2950462963</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="25" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46000.180775463</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>1590</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46006.2645138889</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="s"/>
-      <x:c r="D10" s="22" t="s"/>
-      <x:c r="E10" s="23" t="s"/>
-      <x:c r="F10" s="23" t="s"/>
+      <x:c r="C10" s="26" t="s"/>
+      <x:c r="D10" s="26" t="s"/>
+      <x:c r="E10" s="27" t="s"/>
+      <x:c r="F10" s="27" t="s"/>
     </x:row>
     <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="24" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C11" s="25" t="s"/>
-      <x:c r="D11" s="25" t="s"/>
-      <x:c r="E11" s="25" t="s"/>
-      <x:c r="F11" s="26" t="s">
-        <x:v>33</x:v>
+      <x:c r="B11" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="s"/>
+      <x:c r="D11" s="29" t="s"/>
+      <x:c r="E11" s="29" t="s"/>
+      <x:c r="F11" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="27" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s"/>
-      <x:c r="D12" s="28" t="s"/>
-      <x:c r="E12" s="28" t="s"/>
-      <x:c r="F12" s="29" t="n">
+      <x:c r="B12" s="31" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C12" s="32" t="s"/>
+      <x:c r="D12" s="32" t="s"/>
+      <x:c r="E12" s="32" t="s"/>
+      <x:c r="F12" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="28" t="s"/>
-      <x:c r="F13" s="29" t="n">
+      <x:c r="B13" s="31" t="s">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="s"/>
+      <x:c r="D13" s="32" t="s"/>
+      <x:c r="E13" s="32" t="s"/>
+      <x:c r="F13" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="s"/>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="31" t="s"/>
-      <x:c r="F14" s="32" t="n">
+      <x:c r="B14" s="34" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C14" s="35" t="s"/>
+      <x:c r="D14" s="35" t="s"/>
+      <x:c r="E14" s="35" t="s"/>
+      <x:c r="F14" s="36" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -7947,362 +7977,338 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46031.042974537</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>46015</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216079</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46043.2977199074</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>46029.1168055556</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>45778</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1216071</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46036.0526736111</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C8" s="21" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E8" s="21" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>46034.1687615741</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>45944</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1216081</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>46044.263275463</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="C9" s="21" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F9" s="21" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="G9" s="21" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46031.042974537</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46015</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216079</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46043.2977199074</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
+      <x:c r="H9" s="22">
+        <x:v>46029.112962963</x:v>
+      </x:c>
+      <x:c r="I9" s="23">
+        <x:v>45999</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="n">
+        <x:v>1216072</x:v>
+      </x:c>
+      <x:c r="K9" s="24" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="22">
+        <x:v>46036.0583564815</x:v>
+      </x:c>
+      <x:c r="M9" s="21" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="G10" s="11" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46029.1168055556</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45778</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216071</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46036.0526736111</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
-        <x:v>46034.1687615741</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
+      <x:c r="H10" s="13">
+        <x:v>46034.1741087963</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1216081</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>46044.263275463</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
-        <x:v>46029.112962963</x:v>
-      </x:c>
-      <x:c r="I9" s="18">
-        <x:v>45999</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="n">
-        <x:v>1216072</x:v>
-      </x:c>
-      <x:c r="K9" s="19" t="n">
+      <x:c r="J10" s="12" t="n">
+        <x:v>1216082</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="20">
-        <x:v>46036.0583564815</x:v>
-      </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46034.1741087963</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>45944</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1216082</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="16">
         <x:v>46044.2691666667</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="23" t="s"/>
+      <x:c r="B13" s="25" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="27" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="s">
-        <x:v>33</x:v>
+      <x:c r="B14" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="31" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C15" s="32" t="s"/>
+      <x:c r="D15" s="32" t="s"/>
+      <x:c r="E15" s="32" t="s"/>
+      <x:c r="F15" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="B16" s="31" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C16" s="32" t="s"/>
+      <x:c r="D16" s="32" t="s"/>
+      <x:c r="E16" s="32" t="s"/>
+      <x:c r="F16" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="B17" s="31" t="s">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="s"/>
+      <x:c r="D17" s="32" t="s"/>
+      <x:c r="E17" s="32" t="s"/>
+      <x:c r="F17" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="27" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
+      <x:c r="B18" s="31" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="32" t="s"/>
+      <x:c r="D18" s="32" t="s"/>
+      <x:c r="E18" s="32" t="s"/>
+      <x:c r="F18" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C19" s="31" t="s"/>
-      <x:c r="D19" s="31" t="s"/>
-      <x:c r="E19" s="31" t="s"/>
-      <x:c r="F19" s="32" t="n">
+      <x:c r="B19" s="34" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C19" s="35" t="s"/>
+      <x:c r="D19" s="35" t="s"/>
+      <x:c r="E19" s="35" t="s"/>
+      <x:c r="F19" s="36" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -9366,302 +9372,278 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46050.1475925926</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45988</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216105</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46057.9737731482</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>46066.1502662037</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>46139</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1216135</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46077.9542708333</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C8" s="21" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E8" s="21" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>46066.1892939815</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>45695</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1216131</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>46076.0521180556</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F9" s="21" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="G9" s="21" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46050.1475925926</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45988</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216105</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46057.9737731482</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46066.1502662037</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>46139</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216135</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46077.9542708333</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
-        <x:v>46066.1892939815</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
+      <x:c r="H9" s="22">
+        <x:v>46066.186087963</x:v>
+      </x:c>
+      <x:c r="I9" s="23">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1216131</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
+      <x:c r="J9" s="21" t="n">
+        <x:v>1216130</x:v>
+      </x:c>
+      <x:c r="K9" s="24" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L8" s="20">
-        <x:v>46076.0521180556</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
-        <x:v>46066.186087963</x:v>
-      </x:c>
-      <x:c r="I9" s="18">
-        <x:v>45695</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="n">
-        <x:v>1216130</x:v>
-      </x:c>
-      <x:c r="K9" s="19" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L9" s="22">
         <x:v>46076.0476273148</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="21" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
+      <x:c r="B12" s="25" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C12" s="26" t="s"/>
+      <x:c r="D12" s="26" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="27" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
-        <x:v>33</x:v>
+      <x:c r="B13" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s"/>
+      <x:c r="D13" s="29" t="s"/>
+      <x:c r="E13" s="29" t="s"/>
+      <x:c r="F13" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="31" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C14" s="32" t="s"/>
+      <x:c r="D14" s="32" t="s"/>
+      <x:c r="E14" s="32" t="s"/>
+      <x:c r="F14" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="32" t="s"/>
+      <x:c r="D15" s="32" t="s"/>
+      <x:c r="E15" s="32" t="s"/>
+      <x:c r="F15" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="34" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C16" s="35" t="s"/>
+      <x:c r="D16" s="35" t="s"/>
+      <x:c r="E16" s="35" t="s"/>
+      <x:c r="F16" s="36" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -10726,807 +10708,783 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46072.3153009259</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216162</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46090.311412037</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C7" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E7" s="17" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>46072.0333449074</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1216156</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46090.2584837963</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>46071.1677662037</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1216165</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>46091.1948842593</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F9" s="21" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G9" s="21" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H9" s="22">
+        <x:v>46070.1768402778</x:v>
+      </x:c>
+      <x:c r="I9" s="23">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="n">
+        <x:v>1216138</x:v>
+      </x:c>
+      <x:c r="K9" s="24" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="22">
+        <x:v>46084.1495138889</x:v>
+      </x:c>
+      <x:c r="M9" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46071.3305671296</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1216193</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>46094.1906365741</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>46072.1089467593</x:v>
+      </x:c>
+      <x:c r="I11" s="14">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1216152</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L11" s="16">
+        <x:v>46090.2365046296</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46072.0792939815</x:v>
+      </x:c>
+      <x:c r="I12" s="14">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1216150</x:v>
+      </x:c>
+      <x:c r="K12" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L12" s="16">
+        <x:v>46090.220787037</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46072.0497337963</x:v>
+      </x:c>
+      <x:c r="I13" s="14">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1216148</x:v>
+      </x:c>
+      <x:c r="K13" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L13" s="16">
+        <x:v>46090.2102430556</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46071.2285416667</x:v>
+      </x:c>
+      <x:c r="I14" s="14">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1216143</x:v>
+      </x:c>
+      <x:c r="K14" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L14" s="16">
+        <x:v>46090.0772916667</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I15" s="14">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K15" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L15" s="16">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46079.0151851852</x:v>
+      </x:c>
+      <x:c r="I16" s="14">
+        <x:v>45602</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1216174</x:v>
+      </x:c>
+      <x:c r="K16" s="15" t="n">
+        <x:v>3990</x:v>
+      </x:c>
+      <x:c r="L16" s="16">
+        <x:v>46093.1514351852</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46072.3153009259</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46114</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216162</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="C17" s="11" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H17" s="13">
+        <x:v>46073.0262847222</x:v>
+      </x:c>
+      <x:c r="I17" s="14">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1216157</x:v>
+      </x:c>
+      <x:c r="K17" s="15" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L17" s="16">
+        <x:v>46090.267025463</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H18" s="13">
+        <x:v>46073.0478472222</x:v>
+      </x:c>
+      <x:c r="I18" s="14">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="n">
+        <x:v>1216153</x:v>
+      </x:c>
+      <x:c r="K18" s="15" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L18" s="16">
+        <x:v>46090.2431828704</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H19" s="13">
+        <x:v>46073.1095023148</x:v>
+      </x:c>
+      <x:c r="I19" s="14">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1216164</x:v>
+      </x:c>
+      <x:c r="K19" s="15" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46090.311412037</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="L19" s="16">
+        <x:v>46091.121087963</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46072.0333449074</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216156</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46090.2584837963</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="C20" s="11" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>46073.061099537</x:v>
+      </x:c>
+      <x:c r="I20" s="14">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="n">
+        <x:v>1216151</x:v>
+      </x:c>
+      <x:c r="K20" s="15" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L20" s="16">
+        <x:v>46090.2266435185</x:v>
+      </x:c>
+      <x:c r="M20" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
-        <x:v>46071.1677662037</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1216165</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>46091.1948842593</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="C21" s="11" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I21" s="14">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K21" s="15" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L21" s="16">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M21" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
-        <x:v>46070.1768402778</x:v>
-      </x:c>
-      <x:c r="I9" s="18">
-        <x:v>46123</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="n">
-        <x:v>1216138</x:v>
-      </x:c>
-      <x:c r="K9" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>46084.1495138889</x:v>
-      </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46071.3305671296</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1216193</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
-        <x:v>46094.1906365741</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46072.1089467593</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1216152</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L11" s="20">
-        <x:v>46090.2365046296</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46072.0792939815</x:v>
-      </x:c>
-      <x:c r="I12" s="18">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1216150</x:v>
-      </x:c>
-      <x:c r="K12" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L12" s="20">
-        <x:v>46090.220787037</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46072.0497337963</x:v>
-      </x:c>
-      <x:c r="I13" s="18">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1216148</x:v>
-      </x:c>
-      <x:c r="K13" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L13" s="20">
-        <x:v>46090.2102430556</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46071.2285416667</x:v>
-      </x:c>
-      <x:c r="I14" s="18">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1216143</x:v>
-      </x:c>
-      <x:c r="K14" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L14" s="20">
-        <x:v>46090.0772916667</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46071.2072569444</x:v>
-      </x:c>
-      <x:c r="I15" s="18">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1216142</x:v>
-      </x:c>
-      <x:c r="K15" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L15" s="20">
-        <x:v>46090.0616666667</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46079.0151851852</x:v>
-      </x:c>
-      <x:c r="I16" s="18">
-        <x:v>45602</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1216174</x:v>
-      </x:c>
-      <x:c r="K16" s="19" t="n">
-        <x:v>3990</x:v>
-      </x:c>
-      <x:c r="L16" s="20">
-        <x:v>46093.1514351852</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46073.0262847222</x:v>
-      </x:c>
-      <x:c r="I17" s="18">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1216157</x:v>
-      </x:c>
-      <x:c r="K17" s="19" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L17" s="20">
-        <x:v>46090.267025463</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="C22" s="11" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="D22" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46073.0478472222</x:v>
-      </x:c>
-      <x:c r="I18" s="18">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1216153</x:v>
-      </x:c>
-      <x:c r="K18" s="19" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L18" s="20">
-        <x:v>46090.2431828704</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="F22" s="11" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="G22" s="11" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46073.1095023148</x:v>
-      </x:c>
-      <x:c r="I19" s="18">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1216164</x:v>
-      </x:c>
-      <x:c r="K19" s="19" t="n">
+      <x:c r="H22" s="13">
+        <x:v>46071.2853587963</x:v>
+      </x:c>
+      <x:c r="I22" s="14">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="n">
+        <x:v>1216191</x:v>
+      </x:c>
+      <x:c r="K22" s="15" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L19" s="20">
-        <x:v>46091.121087963</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46073.061099537</x:v>
-      </x:c>
-      <x:c r="I20" s="18">
-        <x:v>46036</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1216151</x:v>
-      </x:c>
-      <x:c r="K20" s="19" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L20" s="20">
-        <x:v>46090.2266435185</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46073.0763541667</x:v>
-      </x:c>
-      <x:c r="I21" s="18">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1216149</x:v>
-      </x:c>
-      <x:c r="K21" s="19" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L21" s="20">
-        <x:v>46090.2162847222</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46071.2853587963</x:v>
-      </x:c>
-      <x:c r="I22" s="18">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1216191</x:v>
-      </x:c>
-      <x:c r="K22" s="19" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L22" s="20">
+      <x:c r="L22" s="16">
         <x:v>46094.1777199074</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M22" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C25" s="22" t="s"/>
-      <x:c r="D25" s="22" t="s"/>
-      <x:c r="E25" s="23" t="s"/>
-      <x:c r="F25" s="23" t="s"/>
+      <x:c r="B25" s="25" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="27" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="24" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C26" s="25" t="s"/>
-      <x:c r="D26" s="25" t="s"/>
-      <x:c r="E26" s="25" t="s"/>
-      <x:c r="F26" s="26" t="s">
-        <x:v>33</x:v>
+      <x:c r="B26" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="27" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C27" s="28" t="s"/>
-      <x:c r="D27" s="28" t="s"/>
-      <x:c r="E27" s="28" t="s"/>
-      <x:c r="F27" s="29" t="n">
+      <x:c r="B27" s="31" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C27" s="32" t="s"/>
+      <x:c r="D27" s="32" t="s"/>
+      <x:c r="E27" s="32" t="s"/>
+      <x:c r="F27" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C28" s="28" t="s"/>
-      <x:c r="D28" s="28" t="s"/>
-      <x:c r="E28" s="28" t="s"/>
-      <x:c r="F28" s="29" t="n">
+      <x:c r="B28" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C28" s="32" t="s"/>
+      <x:c r="D28" s="32" t="s"/>
+      <x:c r="E28" s="32" t="s"/>
+      <x:c r="F28" s="33" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="27" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C29" s="28" t="s"/>
-      <x:c r="D29" s="28" t="s"/>
-      <x:c r="E29" s="28" t="s"/>
-      <x:c r="F29" s="29" t="n">
+      <x:c r="B29" s="31" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C29" s="32" t="s"/>
+      <x:c r="D29" s="32" t="s"/>
+      <x:c r="E29" s="32" t="s"/>
+      <x:c r="F29" s="33" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B30" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C30" s="31" t="s"/>
-      <x:c r="D30" s="31" t="s"/>
-      <x:c r="E30" s="31" t="s"/>
-      <x:c r="F30" s="32" t="n">
+      <x:c r="B30" s="34" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C30" s="35" t="s"/>
+      <x:c r="D30" s="35" t="s"/>
+      <x:c r="E30" s="35" t="s"/>
+      <x:c r="F30" s="36" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -1406,7 +1406,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1476,7 +1476,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>2</x:v>
@@ -2771,7 +2771,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -2841,7 +2841,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>30</x:v>
@@ -4243,7 +4243,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -4313,7 +4313,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="44" t="s"/>
       <x:c r="C7" s="44" t="s"/>
@@ -5499,7 +5499,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -5569,7 +5569,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="44" t="s"/>
       <x:c r="C7" s="44" t="s"/>
@@ -6755,7 +6755,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -6825,7 +6825,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>2</x:v>
@@ -8046,7 +8046,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -8116,7 +8116,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>71</x:v>
@@ -9470,7 +9470,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -9540,7 +9540,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>49</x:v>
@@ -10835,7 +10835,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -10905,7 +10905,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>2</x:v>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -29,12 +29,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>MANUEL NACUA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Ship Station License DOMESTIC Trade (RENEWAL)</x:t>
@@ -527,7 +563,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -572,21 +608,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -596,6 +617,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -846,7 +874,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -857,10 +885,16 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -872,71 +906,53 @@
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -967,120 +983,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1099,16 +1003,76 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1408,18 +1372,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1437,242 +1389,254 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45862.256875</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45908</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215838</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45862.3066319444</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="D7" s="10" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F7" s="17" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G7" s="17" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45861.1595717593</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1215833</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45862.1034606481</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>8</x:v>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G8" s="21" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45862.256875</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45908</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215838</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45862.3066319444</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45861.1595717593</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215833</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45862.1034606481</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45861.1361574074</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1215836</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>7950</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>45862.1391203704</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+      <x:c r="E11" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>45861.181087963</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1215835</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>45862.1344560185</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="25" t="s"/>
-      <x:c r="C10" s="25" t="s"/>
-      <x:c r="D10" s="25" t="s"/>
-      <x:c r="E10" s="25" t="s"/>
-      <x:c r="F10" s="25" t="s"/>
-      <x:c r="G10" s="25" t="s"/>
-      <x:c r="H10" s="25" t="s"/>
-      <x:c r="I10" s="25" t="s"/>
-      <x:c r="J10" s="25" t="s"/>
-      <x:c r="K10" s="25" t="s"/>
-      <x:c r="L10" s="25" t="s"/>
-      <x:c r="M10" s="25" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="25" t="s"/>
-      <x:c r="C11" s="25" t="s"/>
-      <x:c r="D11" s="25" t="s"/>
-      <x:c r="E11" s="25" t="s"/>
-      <x:c r="F11" s="25" t="s"/>
-      <x:c r="G11" s="25" t="s"/>
-      <x:c r="H11" s="25" t="s"/>
-      <x:c r="I11" s="25" t="s"/>
-      <x:c r="J11" s="25" t="s"/>
-      <x:c r="K11" s="25" t="s"/>
-      <x:c r="L11" s="25" t="s"/>
-      <x:c r="M11" s="25" t="s"/>
+      <x:c r="M11" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="28" t="s"/>
+      <x:c r="B14" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="23" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="B15" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="32" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="s"/>
-      <x:c r="D16" s="33" t="s"/>
-      <x:c r="E16" s="33" t="s"/>
-      <x:c r="F16" s="34" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="32" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="s"/>
-      <x:c r="D17" s="33" t="s"/>
-      <x:c r="E17" s="33" t="s"/>
-      <x:c r="F17" s="34" t="n">
+      <x:c r="B17" s="27" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="35" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C18" s="36" t="s"/>
-      <x:c r="D18" s="36" t="s"/>
-      <x:c r="E18" s="36" t="s"/>
-      <x:c r="F18" s="37" t="n">
+      <x:c r="B18" s="30" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="s"/>
+      <x:c r="D18" s="31" t="s"/>
+      <x:c r="E18" s="31" t="s"/>
+      <x:c r="F18" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -2773,18 +2737,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2802,351 +2754,363 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45866.2802893519</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45866.2803009259</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215849</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45873.1184143519</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45875.2238888889</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1215853</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>4030</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45876.2432986111</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G8" s="21" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="D8" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45866.2802893519</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45866.2803009259</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215849</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45873.1184143519</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45875.2238888889</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215853</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>4030</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45876.2432986111</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45875.361724537</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1215851</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>45876.2230902778</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45875.2324652778</x:v>
+      </x:c>
+      <x:c r="I11" s="18">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1215852</x:v>
+      </x:c>
+      <x:c r="K11" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="20">
+        <x:v>45876.2319791667</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45879.4885069444</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1215863</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="L12" s="20">
+        <x:v>45884.277650463</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
-        <x:v>45875.2324652778</x:v>
-      </x:c>
-      <x:c r="I9" s="23">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J9" s="21" t="n">
-        <x:v>1215852</x:v>
-      </x:c>
-      <x:c r="K9" s="24" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L9" s="22">
-        <x:v>45876.2319791667</x:v>
-      </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="38" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="38" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D10" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E10" s="38" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F10" s="38" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G10" s="38" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H10" s="40">
-        <x:v>45879.4885069444</x:v>
-      </x:c>
-      <x:c r="I10" s="41">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J10" s="39" t="n">
-        <x:v>1215863</x:v>
-      </x:c>
-      <x:c r="K10" s="42" t="n">
-        <x:v>1650</x:v>
-      </x:c>
-      <x:c r="L10" s="43">
-        <x:v>45884.277650463</x:v>
-      </x:c>
-      <x:c r="M10" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="38" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C11" s="38" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D11" s="39" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E11" s="38" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F11" s="38" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G11" s="38" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H11" s="40">
+      <x:c r="E13" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
         <x:v>45887.5499305556</x:v>
       </x:c>
-      <x:c r="I11" s="40">
+      <x:c r="I13" s="17">
         <x:v>45887.5499537037</x:v>
       </x:c>
-      <x:c r="J11" s="39" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1215865</x:v>
       </x:c>
-      <x:c r="K11" s="42" t="n">
+      <x:c r="K13" s="19" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="43">
+      <x:c r="L13" s="20">
         <x:v>45891.1027199074</x:v>
       </x:c>
-      <x:c r="M11" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B12" s="25" t="s"/>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="25" t="s"/>
-      <x:c r="G12" s="25" t="s"/>
-      <x:c r="H12" s="25" t="s"/>
-      <x:c r="I12" s="25" t="s"/>
-      <x:c r="J12" s="25" t="s"/>
-      <x:c r="K12" s="25" t="s"/>
-      <x:c r="L12" s="25" t="s"/>
-      <x:c r="M12" s="25" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B13" s="25" t="s"/>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="25" t="s"/>
-      <x:c r="G13" s="25" t="s"/>
-      <x:c r="H13" s="25" t="s"/>
-      <x:c r="I13" s="25" t="s"/>
-      <x:c r="J13" s="25" t="s"/>
-      <x:c r="K13" s="25" t="s"/>
-      <x:c r="L13" s="25" t="s"/>
-      <x:c r="M13" s="25" t="s"/>
+      <x:c r="M13" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="28" t="s"/>
+      <x:c r="B16" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="23" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="B17" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="32" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="s"/>
-      <x:c r="D18" s="33" t="s"/>
-      <x:c r="E18" s="33" t="s"/>
-      <x:c r="F18" s="34" t="n">
+      <x:c r="B18" s="27" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="32" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="s"/>
-      <x:c r="D19" s="33" t="s"/>
-      <x:c r="E19" s="33" t="s"/>
-      <x:c r="F19" s="34" t="n">
+      <x:c r="B19" s="27" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="s"/>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="28" t="s"/>
+      <x:c r="F19" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="32" t="s">
+      <x:c r="B20" s="27" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C20" s="28" t="s"/>
+      <x:c r="D20" s="28" t="s"/>
+      <x:c r="E20" s="28" t="s"/>
+      <x:c r="F20" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="27" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C22" s="28" t="s"/>
+      <x:c r="D22" s="28" t="s"/>
+      <x:c r="E22" s="28" t="s"/>
+      <x:c r="F22" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="30" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C20" s="33" t="s"/>
-      <x:c r="D20" s="33" t="s"/>
-      <x:c r="E20" s="33" t="s"/>
-      <x:c r="F20" s="34" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="32" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="s"/>
-      <x:c r="D21" s="33" t="s"/>
-      <x:c r="E21" s="33" t="s"/>
-      <x:c r="F21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="32" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="s"/>
-      <x:c r="D22" s="33" t="s"/>
-      <x:c r="E22" s="33" t="s"/>
-      <x:c r="F22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="35" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C23" s="36" t="s"/>
-      <x:c r="D23" s="36" t="s"/>
-      <x:c r="E23" s="36" t="s"/>
-      <x:c r="F23" s="37" t="n">
+      <x:c r="C23" s="31" t="s"/>
+      <x:c r="D23" s="31" t="s"/>
+      <x:c r="E23" s="31" t="s"/>
+      <x:c r="F23" s="32" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4245,18 +4209,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4274,75 +4226,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45887.2917592593</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215880</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45903.1177546296</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="44" t="s"/>
-      <x:c r="C7" s="44" t="s"/>
-      <x:c r="D7" s="44" t="s"/>
-      <x:c r="E7" s="44" t="s"/>
-      <x:c r="F7" s="44" t="s"/>
-      <x:c r="G7" s="44" t="s"/>
-      <x:c r="H7" s="44" t="s"/>
-      <x:c r="I7" s="44" t="s"/>
-      <x:c r="J7" s="44" t="s"/>
-      <x:c r="K7" s="44" t="s"/>
-      <x:c r="L7" s="44" t="s"/>
-      <x:c r="M7" s="44" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="45" t="s"/>
-      <x:c r="C8" s="45" t="s"/>
-      <x:c r="D8" s="45" t="s"/>
-      <x:c r="E8" s="45" t="s"/>
-      <x:c r="F8" s="45" t="s"/>
-      <x:c r="G8" s="45" t="s"/>
-      <x:c r="H8" s="45" t="s"/>
-      <x:c r="I8" s="45" t="s"/>
-      <x:c r="J8" s="45" t="s"/>
-      <x:c r="K8" s="45" t="s"/>
-      <x:c r="L8" s="45" t="s"/>
-      <x:c r="M8" s="45" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45887.2917592593</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215880</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45903.1177546296</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -4360,44 +4324,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="26" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="27" t="s"/>
-      <x:c r="D11" s="27" t="s"/>
-      <x:c r="E11" s="28" t="s"/>
-      <x:c r="F11" s="28" t="s"/>
+      <x:c r="B11" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="23" t="s"/>
+      <x:c r="F11" s="23" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C12" s="30" t="s"/>
-      <x:c r="D12" s="30" t="s"/>
-      <x:c r="E12" s="30" t="s"/>
-      <x:c r="F12" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="B12" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="32" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="s"/>
-      <x:c r="D13" s="33" t="s"/>
-      <x:c r="E13" s="33" t="s"/>
-      <x:c r="F13" s="34" t="n">
+      <x:c r="B13" s="27" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C13" s="28" t="s"/>
+      <x:c r="D13" s="28" t="s"/>
+      <x:c r="E13" s="28" t="s"/>
+      <x:c r="F13" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="35" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="36" t="s"/>
-      <x:c r="D14" s="36" t="s"/>
-      <x:c r="E14" s="36" t="s"/>
-      <x:c r="F14" s="37" t="n">
+      <x:c r="B14" s="30" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="31" t="s"/>
+      <x:c r="D14" s="31" t="s"/>
+      <x:c r="E14" s="31" t="s"/>
+      <x:c r="F14" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -5501,18 +5465,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5530,75 +5482,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45944.1129282407</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215998</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45971.316400463</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="44" t="s"/>
-      <x:c r="C7" s="44" t="s"/>
-      <x:c r="D7" s="44" t="s"/>
-      <x:c r="E7" s="44" t="s"/>
-      <x:c r="F7" s="44" t="s"/>
-      <x:c r="G7" s="44" t="s"/>
-      <x:c r="H7" s="44" t="s"/>
-      <x:c r="I7" s="44" t="s"/>
-      <x:c r="J7" s="44" t="s"/>
-      <x:c r="K7" s="44" t="s"/>
-      <x:c r="L7" s="44" t="s"/>
-      <x:c r="M7" s="44" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="45" t="s"/>
-      <x:c r="C8" s="45" t="s"/>
-      <x:c r="D8" s="45" t="s"/>
-      <x:c r="E8" s="45" t="s"/>
-      <x:c r="F8" s="45" t="s"/>
-      <x:c r="G8" s="45" t="s"/>
-      <x:c r="H8" s="45" t="s"/>
-      <x:c r="I8" s="45" t="s"/>
-      <x:c r="J8" s="45" t="s"/>
-      <x:c r="K8" s="45" t="s"/>
-      <x:c r="L8" s="45" t="s"/>
-      <x:c r="M8" s="45" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45944.1129282407</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215998</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45971.316400463</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -5616,44 +5580,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="26" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="27" t="s"/>
-      <x:c r="D11" s="27" t="s"/>
-      <x:c r="E11" s="28" t="s"/>
-      <x:c r="F11" s="28" t="s"/>
+      <x:c r="B11" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="23" t="s"/>
+      <x:c r="F11" s="23" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C12" s="30" t="s"/>
-      <x:c r="D12" s="30" t="s"/>
-      <x:c r="E12" s="30" t="s"/>
-      <x:c r="F12" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="B12" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="32" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="s"/>
-      <x:c r="D13" s="33" t="s"/>
-      <x:c r="E13" s="33" t="s"/>
-      <x:c r="F13" s="34" t="n">
+      <x:c r="B13" s="27" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C13" s="28" t="s"/>
+      <x:c r="D13" s="28" t="s"/>
+      <x:c r="E13" s="28" t="s"/>
+      <x:c r="F13" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="35" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="36" t="s"/>
-      <x:c r="D14" s="36" t="s"/>
-      <x:c r="E14" s="36" t="s"/>
-      <x:c r="F14" s="37" t="n">
+      <x:c r="B14" s="30" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="31" t="s"/>
+      <x:c r="D14" s="31" t="s"/>
+      <x:c r="E14" s="31" t="s"/>
+      <x:c r="F14" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -6757,18 +6721,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6786,166 +6738,178 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46000.4750694444</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45992</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216048</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>744</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46013.2950462963</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46000.4750694444</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216048</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46013.2950462963</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
         <x:v>46000.180775463</x:v>
       </x:c>
-      <x:c r="I7" s="19">
+      <x:c r="I9" s="13">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J7" s="17" t="n">
+      <x:c r="J9" s="11" t="n">
         <x:v>1216037</x:v>
       </x:c>
-      <x:c r="K7" s="20" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L7" s="18">
+      <x:c r="L9" s="12">
         <x:v>46006.2645138889</x:v>
       </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
-      <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="45" t="s"/>
-      <x:c r="C8" s="45" t="s"/>
-      <x:c r="D8" s="45" t="s"/>
-      <x:c r="E8" s="45" t="s"/>
-      <x:c r="F8" s="45" t="s"/>
-      <x:c r="G8" s="45" t="s"/>
-      <x:c r="H8" s="45" t="s"/>
-      <x:c r="I8" s="45" t="s"/>
-      <x:c r="J8" s="45" t="s"/>
-      <x:c r="K8" s="45" t="s"/>
-      <x:c r="L8" s="45" t="s"/>
-      <x:c r="M8" s="45" t="s"/>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="45" t="s"/>
-      <x:c r="C9" s="45" t="s"/>
-      <x:c r="D9" s="45" t="s"/>
-      <x:c r="E9" s="45" t="s"/>
-      <x:c r="F9" s="45" t="s"/>
-      <x:c r="G9" s="45" t="s"/>
-      <x:c r="H9" s="45" t="s"/>
-      <x:c r="I9" s="45" t="s"/>
-      <x:c r="J9" s="45" t="s"/>
-      <x:c r="K9" s="45" t="s"/>
-      <x:c r="L9" s="45" t="s"/>
-      <x:c r="M9" s="45" t="s"/>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="26" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="28" t="s"/>
-      <x:c r="F12" s="28" t="s"/>
+      <x:c r="B12" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="23" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C13" s="30" t="s"/>
-      <x:c r="D13" s="30" t="s"/>
-      <x:c r="E13" s="30" t="s"/>
-      <x:c r="F13" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="B13" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="32" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="s"/>
-      <x:c r="D14" s="33" t="s"/>
-      <x:c r="E14" s="33" t="s"/>
-      <x:c r="F14" s="34" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="32" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="s"/>
-      <x:c r="D15" s="33" t="s"/>
-      <x:c r="E15" s="33" t="s"/>
-      <x:c r="F15" s="34" t="n">
+      <x:c r="B15" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="35" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C16" s="36" t="s"/>
-      <x:c r="D16" s="36" t="s"/>
-      <x:c r="E16" s="36" t="s"/>
-      <x:c r="F16" s="37" t="n">
+      <x:c r="B16" s="30" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8048,18 +8012,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -8077,302 +8029,314 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46031.042974537</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>46015</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216079</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46043.2977199074</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46029.1168055556</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>45778</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1216071</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46036.0526736111</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>76</x:v>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
+      <x:c r="B8" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G8" s="21" t="s">
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="F8" s="11" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46031.042974537</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>46015</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216079</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46043.2977199074</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46029.1168055556</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45778</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216071</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46036.0526736111</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46034.1687615741</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1216081</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>46044.263275463</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+      <x:c r="E11" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>46029.112962963</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>45999</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1216072</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>46036.0583564815</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="38" t="s">
+      <x:c r="M11" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C10" s="38" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D10" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E10" s="38" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F10" s="38" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G10" s="38" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H10" s="40">
+      <x:c r="E12" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
         <x:v>46034.1741087963</x:v>
       </x:c>
-      <x:c r="I10" s="41">
+      <x:c r="I12" s="18">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>1216082</x:v>
       </x:c>
-      <x:c r="K10" s="42" t="n">
+      <x:c r="K12" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L10" s="43">
+      <x:c r="L12" s="20">
         <x:v>46044.2691666667</x:v>
       </x:c>
-      <x:c r="M10" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="25" t="s"/>
-      <x:c r="C11" s="25" t="s"/>
-      <x:c r="D11" s="25" t="s"/>
-      <x:c r="E11" s="25" t="s"/>
-      <x:c r="F11" s="25" t="s"/>
-      <x:c r="G11" s="25" t="s"/>
-      <x:c r="H11" s="25" t="s"/>
-      <x:c r="I11" s="25" t="s"/>
-      <x:c r="J11" s="25" t="s"/>
-      <x:c r="K11" s="25" t="s"/>
-      <x:c r="L11" s="25" t="s"/>
-      <x:c r="M11" s="25" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B12" s="25" t="s"/>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="25" t="s"/>
-      <x:c r="G12" s="25" t="s"/>
-      <x:c r="H12" s="25" t="s"/>
-      <x:c r="I12" s="25" t="s"/>
-      <x:c r="J12" s="25" t="s"/>
-      <x:c r="K12" s="25" t="s"/>
-      <x:c r="L12" s="25" t="s"/>
-      <x:c r="M12" s="25" t="s"/>
+      <x:c r="M12" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="28" t="s"/>
+      <x:c r="B15" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="23" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="B16" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="32" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="s"/>
-      <x:c r="D17" s="33" t="s"/>
-      <x:c r="E17" s="33" t="s"/>
-      <x:c r="F17" s="34" t="n">
+      <x:c r="B17" s="27" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="32" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="s"/>
-      <x:c r="D18" s="33" t="s"/>
-      <x:c r="E18" s="33" t="s"/>
-      <x:c r="F18" s="34" t="n">
+      <x:c r="B18" s="27" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="32" t="s">
+      <x:c r="B19" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="s"/>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="28" t="s"/>
+      <x:c r="F19" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="27" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C20" s="28" t="s"/>
+      <x:c r="D20" s="28" t="s"/>
+      <x:c r="E20" s="28" t="s"/>
+      <x:c r="F20" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C19" s="33" t="s"/>
-      <x:c r="D19" s="33" t="s"/>
-      <x:c r="E19" s="33" t="s"/>
-      <x:c r="F19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="32" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="s"/>
-      <x:c r="D20" s="33" t="s"/>
-      <x:c r="E20" s="33" t="s"/>
-      <x:c r="F20" s="34" t="n">
-        <x:v>2</x:v>
-      </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="35" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C21" s="36" t="s"/>
-      <x:c r="D21" s="36" t="s"/>
-      <x:c r="E21" s="36" t="s"/>
-      <x:c r="F21" s="37" t="n">
+      <x:c r="B21" s="30" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C21" s="31" t="s"/>
+      <x:c r="D21" s="31" t="s"/>
+      <x:c r="E21" s="31" t="s"/>
+      <x:c r="F21" s="32" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -9472,18 +9436,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9501,242 +9453,254 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46050.1475925926</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45988</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216105</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46057.9737731482</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46066.1502662037</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>46139</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1216135</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46077.9542708333</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G8" s="21" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="B8" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46050.1475925926</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45988</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216105</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46057.9737731482</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46066.1502662037</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46139</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216135</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46077.9542708333</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46066.1892939815</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1216131</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>46076.0521180556</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>46066.186087963</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1216130</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>46076.0476273148</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="25" t="s"/>
-      <x:c r="C10" s="25" t="s"/>
-      <x:c r="D10" s="25" t="s"/>
-      <x:c r="E10" s="25" t="s"/>
-      <x:c r="F10" s="25" t="s"/>
-      <x:c r="G10" s="25" t="s"/>
-      <x:c r="H10" s="25" t="s"/>
-      <x:c r="I10" s="25" t="s"/>
-      <x:c r="J10" s="25" t="s"/>
-      <x:c r="K10" s="25" t="s"/>
-      <x:c r="L10" s="25" t="s"/>
-      <x:c r="M10" s="25" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="25" t="s"/>
-      <x:c r="C11" s="25" t="s"/>
-      <x:c r="D11" s="25" t="s"/>
-      <x:c r="E11" s="25" t="s"/>
-      <x:c r="F11" s="25" t="s"/>
-      <x:c r="G11" s="25" t="s"/>
-      <x:c r="H11" s="25" t="s"/>
-      <x:c r="I11" s="25" t="s"/>
-      <x:c r="J11" s="25" t="s"/>
-      <x:c r="K11" s="25" t="s"/>
-      <x:c r="L11" s="25" t="s"/>
-      <x:c r="M11" s="25" t="s"/>
+      <x:c r="M11" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="28" t="s"/>
+      <x:c r="B14" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="23" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="B15" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="32" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="s"/>
-      <x:c r="D16" s="33" t="s"/>
-      <x:c r="E16" s="33" t="s"/>
-      <x:c r="F16" s="34" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="32" t="s">
+      <x:c r="B17" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C17" s="33" t="s"/>
-      <x:c r="D17" s="33" t="s"/>
-      <x:c r="E17" s="33" t="s"/>
-      <x:c r="F17" s="34" t="n">
-        <x:v>2</x:v>
-      </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="35" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C18" s="36" t="s"/>
-      <x:c r="D18" s="36" t="s"/>
-      <x:c r="E18" s="36" t="s"/>
-      <x:c r="F18" s="37" t="n">
+      <x:c r="B18" s="30" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="s"/>
+      <x:c r="D18" s="31" t="s"/>
+      <x:c r="E18" s="31" t="s"/>
+      <x:c r="F18" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -10837,18 +10801,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -10866,747 +10818,759 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46072.3153009259</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>46114</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216162</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46090.311412037</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46072.0333449074</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1216156</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46090.2584837963</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="G8" s="21" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="B8" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46072.3153009259</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216162</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46090.311412037</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46072.0333449074</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216156</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46090.2584837963</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46071.1677662037</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1216165</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>46091.1948842593</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>46070.1768402778</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1216138</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>46084.1495138889</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="38" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="38" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D10" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E10" s="38" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="F10" s="38" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G10" s="38" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H10" s="40">
+      <x:c r="M11" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
         <x:v>46071.3305671296</x:v>
       </x:c>
-      <x:c r="I10" s="41">
+      <x:c r="I12" s="18">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>1216193</x:v>
       </x:c>
-      <x:c r="K10" s="42" t="n">
+      <x:c r="K12" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="43">
+      <x:c r="L12" s="20">
         <x:v>46094.1906365741</x:v>
       </x:c>
-      <x:c r="M10" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="38" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="38" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D11" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E11" s="38" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="F11" s="38" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G11" s="38" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H11" s="40">
+      <x:c r="M12" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
         <x:v>46072.1089467593</x:v>
       </x:c>
-      <x:c r="I11" s="41">
+      <x:c r="I13" s="18">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J11" s="39" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1216152</x:v>
       </x:c>
-      <x:c r="K11" s="42" t="n">
+      <x:c r="K13" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="43">
+      <x:c r="L13" s="20">
         <x:v>46090.2365046296</x:v>
       </x:c>
-      <x:c r="M11" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="38" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="38" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E12" s="38" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="F12" s="38" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G12" s="38" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="H12" s="40">
+      <x:c r="M13" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
         <x:v>46072.0792939815</x:v>
       </x:c>
-      <x:c r="I12" s="41">
+      <x:c r="I14" s="18">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J14" s="16" t="n">
         <x:v>1216150</x:v>
       </x:c>
-      <x:c r="K12" s="42" t="n">
+      <x:c r="K14" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L12" s="43">
+      <x:c r="L14" s="20">
         <x:v>46090.220787037</x:v>
       </x:c>
-      <x:c r="M12" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="38" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="38" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D13" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E13" s="38" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F13" s="38" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G13" s="38" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H13" s="40">
+      <x:c r="M14" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
         <x:v>46072.0497337963</x:v>
       </x:c>
-      <x:c r="I13" s="41">
+      <x:c r="I15" s="18">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J13" s="39" t="n">
+      <x:c r="J15" s="16" t="n">
         <x:v>1216148</x:v>
       </x:c>
-      <x:c r="K13" s="42" t="n">
+      <x:c r="K15" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="43">
+      <x:c r="L15" s="20">
         <x:v>46090.2102430556</x:v>
       </x:c>
-      <x:c r="M13" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="38" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="38" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D14" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E14" s="38" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="F14" s="38" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G14" s="38" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H14" s="40">
+      <x:c r="M15" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
         <x:v>46071.2285416667</x:v>
       </x:c>
-      <x:c r="I14" s="41">
+      <x:c r="I16" s="18">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J16" s="16" t="n">
         <x:v>1216143</x:v>
       </x:c>
-      <x:c r="K14" s="42" t="n">
+      <x:c r="K16" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="43">
+      <x:c r="L16" s="20">
         <x:v>46090.0772916667</x:v>
       </x:c>
-      <x:c r="M14" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="38" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="38" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D15" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E15" s="38" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F15" s="38" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G15" s="38" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="H15" s="40">
+      <x:c r="M16" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
         <x:v>46071.2072569444</x:v>
       </x:c>
-      <x:c r="I15" s="41">
+      <x:c r="I17" s="18">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J15" s="39" t="n">
+      <x:c r="J17" s="16" t="n">
         <x:v>1216142</x:v>
       </x:c>
-      <x:c r="K15" s="42" t="n">
+      <x:c r="K17" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="43">
+      <x:c r="L17" s="20">
         <x:v>46090.0616666667</x:v>
       </x:c>
-      <x:c r="M15" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="38" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="38" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D16" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E16" s="38" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="F16" s="38" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="G16" s="38" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="H16" s="40">
+      <x:c r="M17" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
         <x:v>46079.0151851852</x:v>
       </x:c>
-      <x:c r="I16" s="41">
+      <x:c r="I18" s="18">
         <x:v>45602</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J18" s="16" t="n">
         <x:v>1216174</x:v>
       </x:c>
-      <x:c r="K16" s="42" t="n">
+      <x:c r="K18" s="19" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L16" s="43">
+      <x:c r="L18" s="20">
         <x:v>46093.1514351852</x:v>
       </x:c>
-      <x:c r="M16" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="38" t="s">
+      <x:c r="M18" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C17" s="38" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D17" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E17" s="38" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="F17" s="38" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="G17" s="38" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="H17" s="40">
+      <x:c r="E19" s="15" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
         <x:v>46073.0262847222</x:v>
       </x:c>
-      <x:c r="I17" s="41">
+      <x:c r="I19" s="18">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J17" s="39" t="n">
+      <x:c r="J19" s="16" t="n">
         <x:v>1216157</x:v>
       </x:c>
-      <x:c r="K17" s="42" t="n">
+      <x:c r="K19" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L17" s="43">
+      <x:c r="L19" s="20">
         <x:v>46090.267025463</x:v>
       </x:c>
-      <x:c r="M17" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="38" t="s">
+      <x:c r="M19" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C18" s="38" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D18" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E18" s="38" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F18" s="38" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="G18" s="38" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="H18" s="40">
+      <x:c r="E20" s="15" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
         <x:v>46073.0478472222</x:v>
       </x:c>
-      <x:c r="I18" s="41">
+      <x:c r="I20" s="18">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J20" s="16" t="n">
         <x:v>1216153</x:v>
       </x:c>
-      <x:c r="K18" s="42" t="n">
+      <x:c r="K20" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L18" s="43">
+      <x:c r="L20" s="20">
         <x:v>46090.2431828704</x:v>
       </x:c>
-      <x:c r="M18" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="38" t="s">
+      <x:c r="M20" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C19" s="38" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D19" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E19" s="38" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F19" s="38" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="G19" s="38" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="H19" s="40">
+      <x:c r="E21" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
         <x:v>46073.1095023148</x:v>
       </x:c>
-      <x:c r="I19" s="41">
+      <x:c r="I21" s="18">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J19" s="39" t="n">
+      <x:c r="J21" s="16" t="n">
         <x:v>1216164</x:v>
       </x:c>
-      <x:c r="K19" s="42" t="n">
+      <x:c r="K21" s="19" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L19" s="43">
+      <x:c r="L21" s="20">
         <x:v>46091.121087963</x:v>
       </x:c>
-      <x:c r="M19" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="38" t="s">
+      <x:c r="M21" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C20" s="38" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D20" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E20" s="38" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F20" s="38" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G20" s="38" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H20" s="40">
+      <x:c r="E22" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
         <x:v>46073.061099537</x:v>
       </x:c>
-      <x:c r="I20" s="41">
+      <x:c r="I22" s="18">
         <x:v>46036</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J22" s="16" t="n">
         <x:v>1216151</x:v>
       </x:c>
-      <x:c r="K20" s="42" t="n">
+      <x:c r="K22" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L20" s="43">
+      <x:c r="L22" s="20">
         <x:v>46090.2266435185</x:v>
       </x:c>
-      <x:c r="M20" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="38" t="s">
+      <x:c r="M22" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C21" s="38" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D21" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E21" s="38" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F21" s="38" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G21" s="38" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H21" s="40">
+      <x:c r="E23" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
         <x:v>46073.0763541667</x:v>
       </x:c>
-      <x:c r="I21" s="41">
+      <x:c r="I23" s="18">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J21" s="39" t="n">
+      <x:c r="J23" s="16" t="n">
         <x:v>1216149</x:v>
       </x:c>
-      <x:c r="K21" s="42" t="n">
+      <x:c r="K23" s="19" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L21" s="43">
+      <x:c r="L23" s="20">
         <x:v>46090.2162847222</x:v>
       </x:c>
-      <x:c r="M21" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="38" t="s">
+      <x:c r="M23" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C22" s="38" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D22" s="39" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E22" s="38" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F22" s="38" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G22" s="38" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H22" s="40">
+      <x:c r="E24" s="15" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
         <x:v>46071.2853587963</x:v>
       </x:c>
-      <x:c r="I22" s="41">
+      <x:c r="I24" s="18">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J24" s="16" t="n">
         <x:v>1216191</x:v>
       </x:c>
-      <x:c r="K22" s="42" t="n">
+      <x:c r="K24" s="19" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L22" s="43">
+      <x:c r="L24" s="20">
         <x:v>46094.1777199074</x:v>
       </x:c>
-      <x:c r="M22" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B23" s="25" t="s"/>
-      <x:c r="C23" s="25" t="s"/>
-      <x:c r="D23" s="25" t="s"/>
-      <x:c r="E23" s="25" t="s"/>
-      <x:c r="F23" s="25" t="s"/>
-      <x:c r="G23" s="25" t="s"/>
-      <x:c r="H23" s="25" t="s"/>
-      <x:c r="I23" s="25" t="s"/>
-      <x:c r="J23" s="25" t="s"/>
-      <x:c r="K23" s="25" t="s"/>
-      <x:c r="L23" s="25" t="s"/>
-      <x:c r="M23" s="25" t="s"/>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B24" s="25" t="s"/>
-      <x:c r="C24" s="25" t="s"/>
-      <x:c r="D24" s="25" t="s"/>
-      <x:c r="E24" s="25" t="s"/>
-      <x:c r="F24" s="25" t="s"/>
-      <x:c r="G24" s="25" t="s"/>
-      <x:c r="H24" s="25" t="s"/>
-      <x:c r="I24" s="25" t="s"/>
-      <x:c r="J24" s="25" t="s"/>
-      <x:c r="K24" s="25" t="s"/>
-      <x:c r="L24" s="25" t="s"/>
-      <x:c r="M24" s="25" t="s"/>
+      <x:c r="M24" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="26" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="28" t="s"/>
-      <x:c r="F27" s="28" t="s"/>
+      <x:c r="B27" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C27" s="22" t="s"/>
+      <x:c r="D27" s="22" t="s"/>
+      <x:c r="E27" s="23" t="s"/>
+      <x:c r="F27" s="23" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C28" s="30" t="s"/>
-      <x:c r="D28" s="30" t="s"/>
-      <x:c r="E28" s="30" t="s"/>
-      <x:c r="F28" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="B28" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C28" s="25" t="s"/>
+      <x:c r="D28" s="25" t="s"/>
+      <x:c r="E28" s="25" t="s"/>
+      <x:c r="F28" s="26" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="32" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C29" s="33" t="s"/>
-      <x:c r="D29" s="33" t="s"/>
-      <x:c r="E29" s="33" t="s"/>
-      <x:c r="F29" s="34" t="n">
+      <x:c r="B29" s="27" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C29" s="28" t="s"/>
+      <x:c r="D29" s="28" t="s"/>
+      <x:c r="E29" s="28" t="s"/>
+      <x:c r="F29" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="32" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C30" s="33" t="s"/>
-      <x:c r="D30" s="33" t="s"/>
-      <x:c r="E30" s="33" t="s"/>
-      <x:c r="F30" s="34" t="n">
+      <x:c r="B30" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C30" s="28" t="s"/>
+      <x:c r="D30" s="28" t="s"/>
+      <x:c r="E30" s="28" t="s"/>
+      <x:c r="F30" s="29" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="32" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C31" s="33" t="s"/>
-      <x:c r="D31" s="33" t="s"/>
-      <x:c r="E31" s="33" t="s"/>
-      <x:c r="F31" s="34" t="n">
+      <x:c r="B31" s="27" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C31" s="28" t="s"/>
+      <x:c r="D31" s="28" t="s"/>
+      <x:c r="E31" s="28" t="s"/>
+      <x:c r="F31" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="35" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C32" s="36" t="s"/>
-      <x:c r="D32" s="36" t="s"/>
-      <x:c r="E32" s="36" t="s"/>
-      <x:c r="F32" s="37" t="n">
+      <x:c r="B32" s="30" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C32" s="31" t="s"/>
+      <x:c r="D32" s="31" t="s"/>
+      <x:c r="E32" s="31" t="s"/>
+      <x:c r="F32" s="32" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -37,6 +37,9 @@
     <x:t>MANUEL NACUA</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | July 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -139,6 +142,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | August 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -214,6 +220,9 @@
     <x:t>61-8-2025-1128</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | September 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -229,6 +238,9 @@
     <x:t>61-8-2025-1127</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | November 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGAPITO PERATER BERALLO</x:t>
   </x:si>
   <x:si>
@@ -241,6 +253,9 @@
     <x:t>61-10-2025-1192</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | December 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur Radio Station License (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -268,6 +283,9 @@
     <x:t>61-12-2025-1258-218</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | January 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARENIE CAJETAS FLORA</x:t>
   </x:si>
   <x:si>
@@ -325,6 +343,9 @@
     <x:t>61-1-2026-1273-054</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>EMELIO LUZON PANOY</x:t>
   </x:si>
   <x:si>
@@ -365,6 +386,9 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1327-547</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>ARTURO D ANTONIO</x:t>
@@ -563,7 +587,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -603,6 +627,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -874,12 +922,21 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -894,65 +951,65 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -983,95 +1040,107 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1300,58 +1369,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -1394,249 +1463,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45862.256875</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>45908</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215838</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45862.3066319444</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45861.1595717593</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1215833</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45862.1034606481</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
-        <x:v>45861.1595717593</x:v>
-      </x:c>
-      <x:c r="I9" s="13">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
-        <x:v>1215833</x:v>
-      </x:c>
-      <x:c r="K9" s="14" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L9" s="12">
-        <x:v>45862.1034606481</x:v>
-      </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="B10" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="F10" s="18" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="G10" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>45861.1361574074</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="21">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>1215836</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="22" t="n">
         <x:v>7950</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="23">
         <x:v>45862.1391203704</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="C11" s="18" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="G11" s="18" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
         <x:v>45861.181087963</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="21">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="19" t="n">
         <x:v>1215835</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="22" t="n">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="23">
         <x:v>45862.1344560185</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M11" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="23" t="s"/>
+      <x:c r="B14" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="26" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="s">
+      <x:c r="B15" s="27" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="B16" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="B17" s="30" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="30" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="32" t="n">
+      <x:c r="B18" s="33" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C18" s="34" t="s"/>
+      <x:c r="D18" s="34" t="s"/>
+      <x:c r="E18" s="34" t="s"/>
+      <x:c r="F18" s="35" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -2619,7 +2688,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
@@ -2665,58 +2734,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -2759,358 +2828,358 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="F8" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45866.2802893519</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>45866.2803009259</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215849</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45873.1184143519</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="F9" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45875.2238888889</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="16">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1215853</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>4030</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>45876.2432986111</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="B10" s="18" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="C10" s="18" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>45875.361724537</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="21">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>1215851</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="22" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="23">
         <x:v>45876.2230902778</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="B11" s="18" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
         <x:v>45875.2324652778</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="21">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="19" t="n">
         <x:v>1215852</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="22" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="23">
         <x:v>45876.2319791667</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M11" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="B12" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="D12" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="F12" s="18" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H12" s="20">
         <x:v>45879.4885069444</x:v>
       </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="I12" s="21">
         <x:v>45888</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="19" t="n">
         <x:v>1215863</x:v>
       </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="K12" s="22" t="n">
         <x:v>1650</x:v>
       </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L12" s="23">
         <x:v>45884.277650463</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M12" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="B13" s="18" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="C13" s="18" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="D13" s="19" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="F13" s="18" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H13" s="20">
         <x:v>45887.5499305556</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="20">
         <x:v>45887.5499537037</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="19" t="n">
         <x:v>1215865</x:v>
       </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="K13" s="22" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="20">
+      <x:c r="L13" s="23">
         <x:v>45891.1027199074</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M13" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="23" t="s"/>
+      <x:c r="B16" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="26" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="24" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="s">
+      <x:c r="B17" s="27" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="27" t="s">
+      <x:c r="B18" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="s"/>
+      <x:c r="D18" s="31" t="s"/>
+      <x:c r="E18" s="31" t="s"/>
+      <x:c r="F18" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="30" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C19" s="31" t="s"/>
+      <x:c r="D19" s="31" t="s"/>
+      <x:c r="E19" s="31" t="s"/>
+      <x:c r="F19" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="30" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C20" s="31" t="s"/>
+      <x:c r="D20" s="31" t="s"/>
+      <x:c r="E20" s="31" t="s"/>
+      <x:c r="F20" s="32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="31" t="s"/>
+      <x:c r="D21" s="31" t="s"/>
+      <x:c r="E21" s="31" t="s"/>
+      <x:c r="F21" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="30" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C22" s="31" t="s"/>
+      <x:c r="D22" s="31" t="s"/>
+      <x:c r="E22" s="31" t="s"/>
+      <x:c r="F22" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="33" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="27" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="27" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C20" s="28" t="s"/>
-      <x:c r="D20" s="28" t="s"/>
-      <x:c r="E20" s="28" t="s"/>
-      <x:c r="F20" s="29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="27" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C22" s="28" t="s"/>
-      <x:c r="D22" s="28" t="s"/>
-      <x:c r="E22" s="28" t="s"/>
-      <x:c r="F22" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="30" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C23" s="31" t="s"/>
-      <x:c r="D23" s="31" t="s"/>
-      <x:c r="E23" s="31" t="s"/>
-      <x:c r="F23" s="32" t="n">
+      <x:c r="C23" s="34" t="s"/>
+      <x:c r="D23" s="34" t="s"/>
+      <x:c r="E23" s="34" t="s"/>
+      <x:c r="F23" s="35" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4088,7 +4157,7 @@
   <x:mergeCells count="11">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
@@ -4137,58 +4206,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -4231,81 +4300,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45887.2917592593</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>45883</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215880</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45903.1177546296</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -4324,44 +4393,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="23" t="s"/>
-      <x:c r="F11" s="23" t="s"/>
+      <x:c r="B11" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="25" t="s"/>
+      <x:c r="D11" s="25" t="s"/>
+      <x:c r="E11" s="26" t="s"/>
+      <x:c r="F11" s="26" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="s">
+      <x:c r="B12" s="27" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="C12" s="28" t="s"/>
+      <x:c r="D12" s="28" t="s"/>
+      <x:c r="E12" s="28" t="s"/>
+      <x:c r="F12" s="29" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="27" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="28" t="s"/>
-      <x:c r="F13" s="29" t="n">
+      <x:c r="B13" s="30" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C13" s="31" t="s"/>
+      <x:c r="D13" s="31" t="s"/>
+      <x:c r="E13" s="31" t="s"/>
+      <x:c r="F13" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="s"/>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="31" t="s"/>
-      <x:c r="F14" s="32" t="n">
+      <x:c r="B14" s="33" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="34" t="s"/>
+      <x:c r="D14" s="34" t="s"/>
+      <x:c r="E14" s="34" t="s"/>
+      <x:c r="F14" s="35" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -5348,7 +5417,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>
@@ -5393,58 +5462,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -5487,81 +5556,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="B8" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45944.1129282407</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>45920</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215998</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45971.316400463</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -5580,44 +5649,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="23" t="s"/>
-      <x:c r="F11" s="23" t="s"/>
+      <x:c r="B11" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="25" t="s"/>
+      <x:c r="D11" s="25" t="s"/>
+      <x:c r="E11" s="26" t="s"/>
+      <x:c r="F11" s="26" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="s">
+      <x:c r="B12" s="27" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="C12" s="28" t="s"/>
+      <x:c r="D12" s="28" t="s"/>
+      <x:c r="E12" s="28" t="s"/>
+      <x:c r="F12" s="29" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="27" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="28" t="s"/>
-      <x:c r="F13" s="29" t="n">
+      <x:c r="B13" s="30" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C13" s="31" t="s"/>
+      <x:c r="D13" s="31" t="s"/>
+      <x:c r="E13" s="31" t="s"/>
+      <x:c r="F13" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="s"/>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="31" t="s"/>
-      <x:c r="F14" s="32" t="n">
+      <x:c r="B14" s="33" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="34" t="s"/>
+      <x:c r="D14" s="34" t="s"/>
+      <x:c r="E14" s="34" t="s"/>
+      <x:c r="F14" s="35" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -6604,7 +6673,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>
@@ -6649,58 +6718,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -6743,173 +6812,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="B8" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46000.4750694444</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216048</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>744</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46013.2950462963</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46000.180775463</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="16">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216037</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46006.2645138889</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
+      <x:c r="B12" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="26" t="s"/>
+      <x:c r="F12" s="26" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
+      <x:c r="B13" s="27" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="C13" s="28" t="s"/>
+      <x:c r="D13" s="28" t="s"/>
+      <x:c r="E13" s="28" t="s"/>
+      <x:c r="F13" s="29" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C14" s="31" t="s"/>
+      <x:c r="D14" s="31" t="s"/>
+      <x:c r="E14" s="31" t="s"/>
+      <x:c r="F14" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="31" t="s"/>
+      <x:c r="D15" s="31" t="s"/>
+      <x:c r="E15" s="31" t="s"/>
+      <x:c r="F15" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="33" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C16" s="34" t="s"/>
+      <x:c r="D16" s="34" t="s"/>
+      <x:c r="E16" s="34" t="s"/>
+      <x:c r="F16" s="35" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -7894,7 +7963,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
@@ -7940,58 +8009,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -8034,309 +8103,309 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="B8" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46031.042974537</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>46015</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216079</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46043.2977199074</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="B9" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46029.1168055556</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="16">
         <x:v>45778</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216071</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46036.0526736111</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>88</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="B10" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
+        <x:v>46034.1687615741</x:v>
+      </x:c>
+      <x:c r="I10" s="21">
+        <x:v>45944</x:v>
+      </x:c>
+      <x:c r="J10" s="19" t="n">
+        <x:v>1216081</x:v>
+      </x:c>
+      <x:c r="K10" s="22" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L10" s="23">
+        <x:v>46044.263275463</x:v>
+      </x:c>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="18" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46034.1687615741</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="F11" s="18" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
+        <x:v>46029.112962963</x:v>
+      </x:c>
+      <x:c r="I11" s="21">
+        <x:v>45999</x:v>
+      </x:c>
+      <x:c r="J11" s="19" t="n">
+        <x:v>1216072</x:v>
+      </x:c>
+      <x:c r="K11" s="22" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L11" s="23">
+        <x:v>46036.0583564815</x:v>
+      </x:c>
+      <x:c r="M11" s="18" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="18" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D12" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H12" s="20">
+        <x:v>46034.1741087963</x:v>
+      </x:c>
+      <x:c r="I12" s="21">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1216081</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
-        <x:v>46044.263275463</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46029.112962963</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>45999</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1216072</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="J12" s="19" t="n">
+        <x:v>1216082</x:v>
+      </x:c>
+      <x:c r="K12" s="22" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="20">
-        <x:v>46036.0583564815</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46034.1741087963</x:v>
-      </x:c>
-      <x:c r="I12" s="18">
-        <x:v>45944</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1216082</x:v>
-      </x:c>
-      <x:c r="K12" s="19" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L12" s="23">
         <x:v>46044.2691666667</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M12" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="23" t="s"/>
+      <x:c r="B15" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="26" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="24" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="s">
+      <x:c r="B16" s="27" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="B17" s="30" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="27" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
+      <x:c r="B18" s="30" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="s"/>
+      <x:c r="D18" s="31" t="s"/>
+      <x:c r="E18" s="31" t="s"/>
+      <x:c r="F18" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="n">
+      <x:c r="B19" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" s="31" t="s"/>
+      <x:c r="D19" s="31" t="s"/>
+      <x:c r="E19" s="31" t="s"/>
+      <x:c r="F19" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="27" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C20" s="28" t="s"/>
-      <x:c r="D20" s="28" t="s"/>
-      <x:c r="E20" s="28" t="s"/>
-      <x:c r="F20" s="29" t="n">
+      <x:c r="B20" s="30" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C20" s="31" t="s"/>
+      <x:c r="D20" s="31" t="s"/>
+      <x:c r="E20" s="31" t="s"/>
+      <x:c r="F20" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="30" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C21" s="31" t="s"/>
-      <x:c r="D21" s="31" t="s"/>
-      <x:c r="E21" s="31" t="s"/>
-      <x:c r="F21" s="32" t="n">
+      <x:c r="B21" s="33" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C21" s="34" t="s"/>
+      <x:c r="D21" s="34" t="s"/>
+      <x:c r="E21" s="34" t="s"/>
+      <x:c r="F21" s="35" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -9316,7 +9385,7 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B15:F15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
@@ -9364,58 +9433,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -9458,249 +9527,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="B8" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46050.1475925926</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>45988</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216105</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46057.9737731482</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="B9" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46066.1502662037</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="16">
         <x:v>46139</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216135</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46077.9542708333</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="B10" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>46066.1892939815</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="21">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>1216131</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="22" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="23">
         <x:v>46076.0521180556</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="B11" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
         <x:v>46066.186087963</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="21">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="19" t="n">
         <x:v>1216130</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="22" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="23">
         <x:v>46076.0476273148</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M11" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="23" t="s"/>
+      <x:c r="B14" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="26" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="s">
+      <x:c r="B15" s="27" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="B16" s="30" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="B17" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="30" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="32" t="n">
+      <x:c r="B18" s="33" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C18" s="34" t="s"/>
+      <x:c r="D18" s="34" t="s"/>
+      <x:c r="E18" s="34" t="s"/>
+      <x:c r="F18" s="35" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -10683,7 +10752,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
@@ -10729,58 +10798,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -10823,754 +10892,754 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="B8" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46072.3153009259</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>46114</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216162</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46090.311412037</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46072.0333449074</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216156</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46090.2584837963</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="B10" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>46071.1677662037</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="21">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>1216165</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="23">
         <x:v>46091.1948842593</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="B11" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
         <x:v>46070.1768402778</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="21">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="19" t="n">
         <x:v>1216138</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="22" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="23">
         <x:v>46084.1495138889</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M11" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="B12" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D12" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H12" s="20">
         <x:v>46071.3305671296</x:v>
       </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="I12" s="21">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="19" t="n">
         <x:v>1216193</x:v>
       </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="K12" s="22" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L12" s="23">
         <x:v>46094.1906365741</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M12" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="B13" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D13" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H13" s="20">
         <x:v>46072.1089467593</x:v>
       </x:c>
-      <x:c r="I13" s="18">
+      <x:c r="I13" s="21">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="19" t="n">
         <x:v>1216152</x:v>
       </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="K13" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="20">
+      <x:c r="L13" s="23">
         <x:v>46090.2365046296</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M13" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="B14" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D14" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H14" s="20">
         <x:v>46072.0792939815</x:v>
       </x:c>
-      <x:c r="I14" s="18">
+      <x:c r="I14" s="21">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="n">
+      <x:c r="J14" s="19" t="n">
         <x:v>1216150</x:v>
       </x:c>
-      <x:c r="K14" s="19" t="n">
+      <x:c r="K14" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="20">
+      <x:c r="L14" s="23">
         <x:v>46090.220787037</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M14" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="B15" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D15" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F15" s="18" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G15" s="18" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H15" s="20">
         <x:v>46072.0497337963</x:v>
       </x:c>
-      <x:c r="I15" s="18">
+      <x:c r="I15" s="21">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="n">
+      <x:c r="J15" s="19" t="n">
         <x:v>1216148</x:v>
       </x:c>
-      <x:c r="K15" s="19" t="n">
+      <x:c r="K15" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="20">
+      <x:c r="L15" s="23">
         <x:v>46090.2102430556</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M15" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="B16" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D16" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="18" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="F16" s="18" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G16" s="18" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H16" s="20">
         <x:v>46071.2285416667</x:v>
       </x:c>
-      <x:c r="I16" s="18">
+      <x:c r="I16" s="21">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="n">
+      <x:c r="J16" s="19" t="n">
         <x:v>1216143</x:v>
       </x:c>
-      <x:c r="K16" s="19" t="n">
+      <x:c r="K16" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="20">
+      <x:c r="L16" s="23">
         <x:v>46090.0772916667</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M16" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="B17" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D17" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="18" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F17" s="18" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G17" s="18" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H17" s="20">
         <x:v>46071.2072569444</x:v>
       </x:c>
-      <x:c r="I17" s="18">
+      <x:c r="I17" s="21">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="n">
+      <x:c r="J17" s="19" t="n">
         <x:v>1216142</x:v>
       </x:c>
-      <x:c r="K17" s="19" t="n">
+      <x:c r="K17" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L17" s="20">
+      <x:c r="L17" s="23">
         <x:v>46090.0616666667</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M17" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="B18" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D18" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G18" s="18" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H18" s="20">
         <x:v>46079.0151851852</x:v>
       </x:c>
-      <x:c r="I18" s="18">
+      <x:c r="I18" s="21">
         <x:v>45602</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="n">
+      <x:c r="J18" s="19" t="n">
         <x:v>1216174</x:v>
       </x:c>
-      <x:c r="K18" s="19" t="n">
+      <x:c r="K18" s="22" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L18" s="20">
+      <x:c r="L18" s="23">
         <x:v>46093.1514351852</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M18" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="B19" s="18" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C19" s="18" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D19" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="18" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F19" s="18" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G19" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H19" s="20">
         <x:v>46073.0262847222</x:v>
       </x:c>
-      <x:c r="I19" s="18">
+      <x:c r="I19" s="21">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="n">
+      <x:c r="J19" s="19" t="n">
         <x:v>1216157</x:v>
       </x:c>
-      <x:c r="K19" s="19" t="n">
+      <x:c r="K19" s="22" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L19" s="20">
+      <x:c r="L19" s="23">
         <x:v>46090.267025463</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M19" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="B20" s="18" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D20" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E20" s="18" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F20" s="18" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G20" s="18" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H20" s="20">
         <x:v>46073.0478472222</x:v>
       </x:c>
-      <x:c r="I20" s="18">
+      <x:c r="I20" s="21">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="n">
+      <x:c r="J20" s="19" t="n">
         <x:v>1216153</x:v>
       </x:c>
-      <x:c r="K20" s="19" t="n">
+      <x:c r="K20" s="22" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L20" s="20">
+      <x:c r="L20" s="23">
         <x:v>46090.2431828704</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M20" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="B21" s="18" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C21" s="18" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D21" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E21" s="18" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F21" s="18" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G21" s="18" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H21" s="20">
         <x:v>46073.1095023148</x:v>
       </x:c>
-      <x:c r="I21" s="18">
+      <x:c r="I21" s="21">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="n">
+      <x:c r="J21" s="19" t="n">
         <x:v>1216164</x:v>
       </x:c>
-      <x:c r="K21" s="19" t="n">
+      <x:c r="K21" s="22" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L21" s="20">
+      <x:c r="L21" s="23">
         <x:v>46091.121087963</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M21" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="B22" s="18" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C22" s="18" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="D22" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F22" s="18" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G22" s="18" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H22" s="20">
         <x:v>46073.061099537</x:v>
       </x:c>
-      <x:c r="I22" s="18">
+      <x:c r="I22" s="21">
         <x:v>46036</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="n">
+      <x:c r="J22" s="19" t="n">
         <x:v>1216151</x:v>
       </x:c>
-      <x:c r="K22" s="19" t="n">
+      <x:c r="K22" s="22" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L22" s="20">
+      <x:c r="L22" s="23">
         <x:v>46090.2266435185</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M22" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C23" s="15" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
+      <x:c r="B23" s="18" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C23" s="18" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D23" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E23" s="18" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="H23" s="17">
+      <x:c r="F23" s="18" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G23" s="18" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H23" s="20">
         <x:v>46073.0763541667</x:v>
       </x:c>
-      <x:c r="I23" s="18">
+      <x:c r="I23" s="21">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="n">
+      <x:c r="J23" s="19" t="n">
         <x:v>1216149</x:v>
       </x:c>
-      <x:c r="K23" s="19" t="n">
+      <x:c r="K23" s="22" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L23" s="20">
+      <x:c r="L23" s="23">
         <x:v>46090.2162847222</x:v>
       </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M23" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
+      <x:c r="B24" s="18" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C24" s="18" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="D24" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E24" s="18" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F24" s="18" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G24" s="18" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H24" s="20">
         <x:v>46071.2853587963</x:v>
       </x:c>
-      <x:c r="I24" s="18">
+      <x:c r="I24" s="21">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="n">
+      <x:c r="J24" s="19" t="n">
         <x:v>1216191</x:v>
       </x:c>
-      <x:c r="K24" s="19" t="n">
+      <x:c r="K24" s="22" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L24" s="20">
+      <x:c r="L24" s="23">
         <x:v>46094.1777199074</x:v>
       </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>20</x:v>
+      <x:c r="M24" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C27" s="22" t="s"/>
-      <x:c r="D27" s="22" t="s"/>
-      <x:c r="E27" s="23" t="s"/>
-      <x:c r="F27" s="23" t="s"/>
+      <x:c r="B27" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="26" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="24" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C28" s="25" t="s"/>
-      <x:c r="D28" s="25" t="s"/>
-      <x:c r="E28" s="25" t="s"/>
-      <x:c r="F28" s="26" t="s">
+      <x:c r="B28" s="27" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="C28" s="28" t="s"/>
+      <x:c r="D28" s="28" t="s"/>
+      <x:c r="E28" s="28" t="s"/>
+      <x:c r="F28" s="29" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="27" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C29" s="28" t="s"/>
-      <x:c r="D29" s="28" t="s"/>
-      <x:c r="E29" s="28" t="s"/>
-      <x:c r="F29" s="29" t="n">
+      <x:c r="B29" s="30" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C29" s="31" t="s"/>
+      <x:c r="D29" s="31" t="s"/>
+      <x:c r="E29" s="31" t="s"/>
+      <x:c r="F29" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C30" s="28" t="s"/>
-      <x:c r="D30" s="28" t="s"/>
-      <x:c r="E30" s="28" t="s"/>
-      <x:c r="F30" s="29" t="n">
+      <x:c r="B30" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C30" s="31" t="s"/>
+      <x:c r="D30" s="31" t="s"/>
+      <x:c r="E30" s="31" t="s"/>
+      <x:c r="F30" s="32" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="27" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C31" s="28" t="s"/>
-      <x:c r="D31" s="28" t="s"/>
-      <x:c r="E31" s="28" t="s"/>
-      <x:c r="F31" s="29" t="n">
+      <x:c r="B31" s="30" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C31" s="31" t="s"/>
+      <x:c r="D31" s="31" t="s"/>
+      <x:c r="E31" s="31" t="s"/>
+      <x:c r="F31" s="32" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="30" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C32" s="31" t="s"/>
-      <x:c r="D32" s="31" t="s"/>
-      <x:c r="E32" s="31" t="s"/>
-      <x:c r="F32" s="32" t="n">
+      <x:c r="B32" s="33" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C32" s="34" t="s"/>
+      <x:c r="D32" s="34" t="s"/>
+      <x:c r="E32" s="34" t="s"/>
+      <x:c r="F32" s="35" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -12539,7 +12608,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B27:F27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="223">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -94,6 +94,9 @@
     <x:t>61-7-2025-1080</x:t>
   </x:si>
   <x:si>
+    <x:t>1215838</x:t>
+  </x:si>
+  <x:si>
     <x:t>Catalina EBON</x:t>
   </x:si>
   <x:si>
@@ -106,6 +109,9 @@
     <x:t>61-7-2025-1074</x:t>
   </x:si>
   <x:si>
+    <x:t>1215833</x:t>
+  </x:si>
+  <x:si>
     <x:t>FB"GENIZA"/ ELIZA G. LLABAN</x:t>
   </x:si>
   <x:si>
@@ -118,6 +124,9 @@
     <x:t>61-7-2025-1073</x:t>
   </x:si>
   <x:si>
+    <x:t>1215836</x:t>
+  </x:si>
+  <x:si>
     <x:t>Special Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -130,6 +139,9 @@
     <x:t>61-7-2025-1076</x:t>
   </x:si>
   <x:si>
+    <x:t>1215835</x:t>
+  </x:si>
+  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -163,6 +175,9 @@
     <x:t>61-7-2025-1086</x:t>
   </x:si>
   <x:si>
+    <x:t>1215849</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -178,6 +193,9 @@
     <x:t>61-8-2025-1092</x:t>
   </x:si>
   <x:si>
+    <x:t>1215853</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -187,12 +205,18 @@
     <x:t>61-8-2025-1095</x:t>
   </x:si>
   <x:si>
+    <x:t>1215851</x:t>
+  </x:si>
+  <x:si>
     <x:t>MP-ROIX-01007-25</x:t>
   </x:si>
   <x:si>
     <x:t>61-8-2025-1093</x:t>
   </x:si>
   <x:si>
+    <x:t>1215852</x:t>
+  </x:si>
+  <x:si>
     <x:t>LORNA Y. BALONGCAS</x:t>
   </x:si>
   <x:si>
@@ -205,6 +229,9 @@
     <x:t>61-8-2025-1107</x:t>
   </x:si>
   <x:si>
+    <x:t>1215863</x:t>
+  </x:si>
+  <x:si>
     <x:t>Special Radio Operator Certificate (NEW)</x:t>
   </x:si>
   <x:si>
@@ -220,6 +247,9 @@
     <x:t>61-8-2025-1128</x:t>
   </x:si>
   <x:si>
+    <x:t>1215865</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | September 2025</x:t>
   </x:si>
   <x:si>
@@ -238,6 +268,9 @@
     <x:t>61-8-2025-1127</x:t>
   </x:si>
   <x:si>
+    <x:t>1215880</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | November 2025</x:t>
   </x:si>
   <x:si>
@@ -253,6 +286,9 @@
     <x:t>61-10-2025-1192</x:t>
   </x:si>
   <x:si>
+    <x:t>1215998</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | December 2025</x:t>
   </x:si>
   <x:si>
@@ -271,6 +307,9 @@
     <x:t>61-12-2025-1259-416</x:t>
   </x:si>
   <x:si>
+    <x:t>1216048</x:t>
+  </x:si>
+  <x:si>
     <x:t>CRESENCIO C. JUSAY</x:t>
   </x:si>
   <x:si>
@@ -283,6 +322,9 @@
     <x:t>61-12-2025-1258-218</x:t>
   </x:si>
   <x:si>
+    <x:t>1216037</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | January 2026</x:t>
   </x:si>
   <x:si>
@@ -298,6 +340,9 @@
     <x:t>61-1-2026-1269-970</x:t>
   </x:si>
   <x:si>
+    <x:t>1216079</x:t>
+  </x:si>
+  <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -313,6 +358,9 @@
     <x:t>61-1-2026-1268-653</x:t>
   </x:si>
   <x:si>
+    <x:t>1216071</x:t>
+  </x:si>
+  <x:si>
     <x:t>cashier 9</x:t>
   </x:si>
   <x:si>
@@ -328,12 +376,18 @@
     <x:t>61-1-2026-1272-159</x:t>
   </x:si>
   <x:si>
+    <x:t>1216081</x:t>
+  </x:si>
+  <x:si>
     <x:t>93-GOVIX-047</x:t>
   </x:si>
   <x:si>
     <x:t>61-1-2026-1267-387</x:t>
   </x:si>
   <x:si>
+    <x:t>1216072</x:t>
+  </x:si>
+  <x:si>
     <x:t>RAUL GALLEGO DIANAL</x:t>
   </x:si>
   <x:si>
@@ -343,6 +397,9 @@
     <x:t>61-1-2026-1273-054</x:t>
   </x:si>
   <x:si>
+    <x:t>1216082</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | February 2026</x:t>
   </x:si>
   <x:si>
@@ -358,6 +415,9 @@
     <x:t>61-1-2026-1298-673</x:t>
   </x:si>
   <x:si>
+    <x:t>1216105</x:t>
+  </x:si>
+  <x:si>
     <x:t>REYNALDO LUMBATAN ANITO</x:t>
   </x:si>
   <x:si>
@@ -370,6 +430,9 @@
     <x:t>61-2-2026-1323-800</x:t>
   </x:si>
   <x:si>
+    <x:t>1216135</x:t>
+  </x:si>
+  <x:si>
     <x:t>FRANKLIN S. LABOR</x:t>
   </x:si>
   <x:si>
@@ -382,12 +445,18 @@
     <x:t>61-2-2026-1328-050</x:t>
   </x:si>
   <x:si>
+    <x:t>1216131</x:t>
+  </x:si>
+  <x:si>
     <x:t>MS9/FV-1152-21</x:t>
   </x:si>
   <x:si>
     <x:t>61-2-2026-1327-547</x:t>
   </x:si>
   <x:si>
+    <x:t>1216130</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
@@ -403,6 +472,9 @@
     <x:t>61-2-2026-1346-185</x:t>
   </x:si>
   <x:si>
+    <x:t>1216162</x:t>
+  </x:si>
+  <x:si>
     <x:t>AL S. BURBURAN</x:t>
   </x:si>
   <x:si>
@@ -415,6 +487,9 @@
     <x:t>61-2-2026-1340-327</x:t>
   </x:si>
   <x:si>
+    <x:t>1216156</x:t>
+  </x:si>
+  <x:si>
     <x:t>FEY S. BURBURAN</x:t>
   </x:si>
   <x:si>
@@ -427,6 +502,9 @@
     <x:t>61-2-2026-1332-813</x:t>
   </x:si>
   <x:si>
+    <x:t>1216165</x:t>
+  </x:si>
+  <x:si>
     <x:t>JUDELYN B. AMANIA</x:t>
   </x:si>
   <x:si>
@@ -439,6 +517,9 @@
     <x:t>61-2-2026-1331-064</x:t>
   </x:si>
   <x:si>
+    <x:t>1216138</x:t>
+  </x:si>
+  <x:si>
     <x:t>NDC FISHING CORPORATION</x:t>
   </x:si>
   <x:si>
@@ -451,6 +532,9 @@
     <x:t>61-2-2026-1337-307</x:t>
   </x:si>
   <x:si>
+    <x:t>1216193</x:t>
+  </x:si>
+  <x:si>
     <x:t>REMEGIO T. BURBURAN</x:t>
   </x:si>
   <x:si>
@@ -463,6 +547,9 @@
     <x:t>61-2-2026-1344-597</x:t>
   </x:si>
   <x:si>
+    <x:t>1216152</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -472,6 +559,9 @@
     <x:t>61-2-2026-1343-619</x:t>
   </x:si>
   <x:si>
+    <x:t>1216150</x:t>
+  </x:si>
+  <x:si>
     <x:t>REMEGIO T. BURBURAN JR.</x:t>
   </x:si>
   <x:si>
@@ -484,6 +574,9 @@
     <x:t>61-2-2026-1342-435</x:t>
   </x:si>
   <x:si>
+    <x:t>1216148</x:t>
+  </x:si>
+  <x:si>
     <x:t>REY S. BURBURAN</x:t>
   </x:si>
   <x:si>
@@ -493,6 +586,9 @@
     <x:t>61-2-2026-1334-066</x:t>
   </x:si>
   <x:si>
+    <x:t>1216143</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A Prk Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -502,6 +598,9 @@
     <x:t>61-2-2026-1333-303</x:t>
   </x:si>
   <x:si>
+    <x:t>1216142</x:t>
+  </x:si>
+  <x:si>
     <x:t>RHEINT JAY CENO</x:t>
   </x:si>
   <x:si>
@@ -514,6 +613,9 @@
     <x:t>61-2-2026-1372-847</x:t>
   </x:si>
   <x:si>
+    <x:t>1216174</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARCHER C COTINA</x:t>
   </x:si>
   <x:si>
@@ -526,6 +628,9 @@
     <x:t>61-2-2026-1347-156</x:t>
   </x:si>
   <x:si>
+    <x:t>1216157</x:t>
+  </x:si>
+  <x:si>
     <x:t>CLAUDIO E. ELNAR</x:t>
   </x:si>
   <x:si>
@@ -538,6 +643,9 @@
     <x:t>61-2-2026-1348-671</x:t>
   </x:si>
   <x:si>
+    <x:t>1216153</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDGAR S SERENCIO</x:t>
   </x:si>
   <x:si>
@@ -550,6 +658,9 @@
     <x:t>61-2-2026-1351-693</x:t>
   </x:si>
   <x:si>
+    <x:t>1216164</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDWIN M SAGAYNO</x:t>
   </x:si>
   <x:si>
@@ -559,6 +670,9 @@
     <x:t>61-2-2026-1349-935</x:t>
   </x:si>
   <x:si>
+    <x:t>1216151</x:t>
+  </x:si>
+  <x:si>
     <x:t>RAMON M SILVA</x:t>
   </x:si>
   <x:si>
@@ -568,6 +682,9 @@
     <x:t>61-2-2026-1350-437</x:t>
   </x:si>
   <x:si>
+    <x:t>1216149</x:t>
+  </x:si>
+  <x:si>
     <x:t>RODEL PALMERO TOLENTINO</x:t>
   </x:si>
   <x:si>
@@ -578,6 +695,9 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1336-018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216191</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -658,13 +778,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -682,6 +795,13 @@
       <x:sz val="14"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -957,46 +1077,46 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1051,6 +1171,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1062,72 +1186,68 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1507,7 +1627,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
@@ -1519,23 +1639,23 @@
       <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45862.256875</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="H8" s="16">
+        <x:v>45862.2568792245</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45908</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215838</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45862.3066319444</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45862.3066347569</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -1545,165 +1665,165 @@
       <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45861.1595728241</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>45862.1034618403</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45861.1595717593</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1215833</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45862.1034606481</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45861.1361574074</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="F10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45861.1361588889</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1215836</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>7950</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45862.1391203704</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45862.1391293403</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="B11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45861.181087963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E11" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45861.1810907407</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1215835</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45862.1344560185</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L11" s="18">
+        <x:v>45862.1344605671</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="24" t="s"/>
+      <x:c r="B14" s="19" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="B15" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="B17" s="25" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="31" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C18" s="32" t="s"/>
-      <x:c r="D18" s="32" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="33" t="n">
+      <x:c r="B18" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -2804,7 +2924,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2880,317 +3000,317 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45866.2802893519</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45866.2803009259</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215849</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45866.2802922106</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45866.2803013889</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45873.1184143519</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45873.1184145139</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45875.2238915046</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>4030</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>45876.2433041204</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45875.3617282407</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>45876.2230995023</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45875.2324767593</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>45876.2319890162</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45879.4885117361</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>45884.2776561458</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45875.2238888889</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1215853</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>4030</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45876.2432986111</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45875.361724537</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1215851</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45876.2230902778</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45875.2324652778</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1215852</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45876.2319791667</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>45879.4885069444</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1215863</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>1650</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>45884.277650463</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>45887.5499305556</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>45887.5499537037</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1215865</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="E13" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45887.5499379745</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>45887.5499545023</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="21">
-        <x:v>45891.1027199074</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L13" s="18">
+        <x:v>45891.1027280787</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="24" t="s"/>
+      <x:c r="B16" s="19" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="B17" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="25" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="B19" s="25" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="28" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
+      <x:c r="B20" s="25" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="28" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C21" s="29" t="s"/>
-      <x:c r="D21" s="29" t="s"/>
-      <x:c r="E21" s="29" t="s"/>
-      <x:c r="F21" s="30" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="28" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C22" s="29" t="s"/>
-      <x:c r="D22" s="29" t="s"/>
-      <x:c r="E22" s="29" t="s"/>
-      <x:c r="F22" s="30" t="n">
+      <x:c r="B22" s="25" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="31" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C23" s="32" t="s"/>
-      <x:c r="D23" s="32" t="s"/>
-      <x:c r="E23" s="32" t="s"/>
-      <x:c r="F23" s="33" t="n">
+      <x:c r="B23" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C23" s="29" t="s"/>
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="29" t="s"/>
+      <x:c r="F23" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4289,7 +4409,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -4364,41 +4484,41 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="B8" s="31" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45887.2917592593</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="E8" s="31" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F8" s="31" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G8" s="31" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>45887.291765787</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
         <x:v>45883</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215880</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="31" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45903.1177546296</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L8" s="32">
+        <x:v>45903.117765081</x:v>
+      </x:c>
+      <x:c r="M8" s="31" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -4417,44 +4537,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s"/>
-      <x:c r="D11" s="23" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="24" t="s"/>
+      <x:c r="B11" s="19" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="s"/>
+      <x:c r="D11" s="20" t="s"/>
+      <x:c r="E11" s="21" t="s"/>
+      <x:c r="F11" s="21" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" s="26" t="s"/>
-      <x:c r="D12" s="26" t="s"/>
-      <x:c r="E12" s="26" t="s"/>
-      <x:c r="F12" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="B12" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="s"/>
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="24" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s"/>
-      <x:c r="D13" s="29" t="s"/>
-      <x:c r="E13" s="29" t="s"/>
-      <x:c r="F13" s="30" t="n">
+      <x:c r="B13" s="25" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="31" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C14" s="32" t="s"/>
-      <x:c r="D14" s="32" t="s"/>
-      <x:c r="E14" s="32" t="s"/>
-      <x:c r="F14" s="33" t="n">
+      <x:c r="B14" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -5558,7 +5678,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -5633,41 +5753,41 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="B8" s="31" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45944.1129282407</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="E8" s="31" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F8" s="31" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G8" s="31" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
+        <x:v>45944.1129354167</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
         <x:v>45920</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215998</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="31" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45971.316400463</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L8" s="32">
+        <x:v>45971.3164108796</x:v>
+      </x:c>
+      <x:c r="M8" s="31" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -5686,44 +5806,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s"/>
-      <x:c r="D11" s="23" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="24" t="s"/>
+      <x:c r="B11" s="19" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="s"/>
+      <x:c r="D11" s="20" t="s"/>
+      <x:c r="E11" s="21" t="s"/>
+      <x:c r="F11" s="21" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" s="26" t="s"/>
-      <x:c r="D12" s="26" t="s"/>
-      <x:c r="E12" s="26" t="s"/>
-      <x:c r="F12" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="B12" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="s"/>
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="24" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s"/>
-      <x:c r="D13" s="29" t="s"/>
-      <x:c r="E13" s="29" t="s"/>
-      <x:c r="F13" s="30" t="n">
+      <x:c r="B13" s="25" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="31" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C14" s="32" t="s"/>
-      <x:c r="D14" s="32" t="s"/>
-      <x:c r="E14" s="32" t="s"/>
-      <x:c r="F14" s="33" t="n">
+      <x:c r="B14" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -6827,7 +6947,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -6903,40 +7023,40 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>77</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46000.4750694444</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46000.4750792361</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216048</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>744</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46013.2950462963</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46013.2950574421</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -6944,91 +7064,91 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>82</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46000.180775463</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46000.1807785301</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46006.2645138889</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46006.2645192361</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s"/>
-      <x:c r="D12" s="23" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="24" t="s"/>
+      <x:c r="B12" s="19" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="26" t="s"/>
-      <x:c r="D13" s="26" t="s"/>
-      <x:c r="E13" s="26" t="s"/>
-      <x:c r="F13" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="B13" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s"/>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="30" t="n">
+      <x:c r="B14" s="25" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="28" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="29" t="s"/>
-      <x:c r="F15" s="30" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="31" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C16" s="32" t="s"/>
-      <x:c r="D16" s="32" t="s"/>
-      <x:c r="E16" s="32" t="s"/>
-      <x:c r="F16" s="33" t="n">
+      <x:c r="B16" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8131,7 +8251,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -8207,268 +8327,268 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46031.042974537</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46031.0429770602</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>46015</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216079</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46043.2977199074</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46043.2977226505</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>91</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46029.1168055556</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46029.1168153009</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>45778</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216071</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46036.0526736111</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46036.0526802894</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>94</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46034.1687615741</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="E10" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46034.1687700231</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1216081</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46044.263275463</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46044.2632803241</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="B11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46029.112962963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E11" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46029.1129715509</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>45999</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1216072</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46036.0583564815</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>94</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46036.0583638426</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
+      <x:c r="B12" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46034.1741087963</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="E12" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46034.174115162</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1216082</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="J12" s="15" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46044.2691666667</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L12" s="18">
+        <x:v>46044.2691750116</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="24" t="s"/>
+      <x:c r="B15" s="19" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="21" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="B16" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="B17" s="25" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="25" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="28" t="s">
+      <x:c r="B19" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="28" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
+      <x:c r="B20" s="25" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="31" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C21" s="32" t="s"/>
-      <x:c r="D21" s="32" t="s"/>
-      <x:c r="E21" s="32" t="s"/>
-      <x:c r="F21" s="33" t="n">
+      <x:c r="B21" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C21" s="29" t="s"/>
+      <x:c r="D21" s="29" t="s"/>
+      <x:c r="E21" s="29" t="s"/>
+      <x:c r="F21" s="30" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -9568,7 +9688,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>104</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -9644,208 +9764,208 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>107</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46050.1475925926</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46050.1475945255</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45988</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216105</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46057.9737731482</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46057.9737815278</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46066.1502662037</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46066.1502727199</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46139</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216135</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46077.9542708333</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46077.954281088</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46066.1892939815</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="E10" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46066.1893041088</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1216131</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46076.0521180556</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46076.0521240394</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="C11" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46066.186087963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E11" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46066.1860957755</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1216130</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46076.0476273148</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46076.0476356713</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="24" t="s"/>
+      <x:c r="B14" s="19" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="B15" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="25" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="31" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C18" s="32" t="s"/>
-      <x:c r="D18" s="32" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="33" t="n">
+      <x:c r="B18" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -10946,7 +11066,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -11022,40 +11142,40 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>122</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46072.3153009259</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46072.3153026736</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>46114</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216162</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46090.311412037</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46090.3114235417</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -11063,672 +11183,672 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46072.0333449074</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46072.0333546991</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216156</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46090.2584837963</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46090.2584930556</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46071.1677662037</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="E10" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46071.1677711806</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1216165</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46091.1948842593</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46091.1948946528</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="C11" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46070.1768402778</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E11" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46070.1768476389</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1216138</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46084.1495138889</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46084.1495253588</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
+      <x:c r="C12" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46071.3305671296</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="E12" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46071.3305731597</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1216193</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="J12" s="15" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46094.1906365741</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L12" s="18">
+        <x:v>46094.1906452199</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
+      <x:c r="C13" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46072.1089467593</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="E13" s="14" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46072.1089512963</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1216152</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="J13" s="15" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46090.2365046296</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L13" s="18">
+        <x:v>46090.2365117824</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
+      <x:c r="C14" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46072.0792939815</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
+      <x:c r="E14" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46072.0792950116</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1216150</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
+      <x:c r="J14" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46090.220787037</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L14" s="18">
+        <x:v>46090.220792662</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
+      <x:c r="C15" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46072.0497337963</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
+      <x:c r="E15" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46072.0497342708</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1216148</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
+      <x:c r="J15" s="15" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46090.2102430556</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L15" s="18">
+        <x:v>46090.2102464352</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
+      <x:c r="C16" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46071.2285416667</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
+      <x:c r="E16" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46071.2285509838</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1216143</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
+      <x:c r="J16" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46090.0772916667</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L16" s="18">
+        <x:v>46090.0772934491</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
+      <x:c r="C17" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46071.2072569444</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="E17" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46071.2072683796</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1216142</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
+      <x:c r="J17" s="15" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46090.0616666667</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L17" s="18">
+        <x:v>46090.0616673032</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
+      <x:c r="C18" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46079.0151851852</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="E18" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46079.0151889352</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
         <x:v>45602</x:v>
       </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1216174</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
+      <x:c r="J18" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46093.1514351852</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L18" s="18">
+        <x:v>46093.1514429977</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
+      <x:c r="B19" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46073.0262847222</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
+      <x:c r="E19" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46073.0262962616</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1216157</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
+      <x:c r="J19" s="15" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46090.267025463</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L19" s="18">
+        <x:v>46090.2670310069</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
+      <x:c r="B20" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46073.0478472222</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
+      <x:c r="E20" s="14" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46073.0478536458</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1216153</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
+      <x:c r="J20" s="15" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46090.2431828704</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L20" s="18">
+        <x:v>46090.2431909954</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s">
+      <x:c r="B21" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E21" s="17" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46073.1095023148</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
+      <x:c r="E21" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46073.10951125</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1216164</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
+      <x:c r="J21" s="15" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46091.121087963</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L21" s="18">
+        <x:v>46091.1210900116</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s">
+      <x:c r="B22" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E22" s="17" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46073.061099537</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
+      <x:c r="E22" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46073.0611031366</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
         <x:v>46036</x:v>
       </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1216151</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
+      <x:c r="J22" s="15" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46090.2266435185</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L22" s="18">
+        <x:v>46090.2266513079</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C23" s="17" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="s">
+      <x:c r="B23" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E23" s="17" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="F23" s="17" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H23" s="19">
-        <x:v>46073.0763541667</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
+      <x:c r="E23" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46073.0763545833</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>1216149</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
+      <x:c r="J23" s="15" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46090.2162847222</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L23" s="18">
+        <x:v>46090.2162962268</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="s">
+      <x:c r="B24" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E24" s="17" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>46071.2853587963</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
+      <x:c r="E24" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46071.2853697569</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1216191</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
+      <x:c r="J24" s="15" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46094.1777199074</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L24" s="18">
+        <x:v>46094.1777229282</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C27" s="23" t="s"/>
-      <x:c r="D27" s="23" t="s"/>
-      <x:c r="E27" s="24" t="s"/>
-      <x:c r="F27" s="24" t="s"/>
+      <x:c r="B27" s="19" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="s"/>
+      <x:c r="D27" s="20" t="s"/>
+      <x:c r="E27" s="21" t="s"/>
+      <x:c r="F27" s="21" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="B28" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C28" s="23" t="s"/>
+      <x:c r="D28" s="23" t="s"/>
+      <x:c r="E28" s="23" t="s"/>
+      <x:c r="F28" s="24" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="28" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C29" s="29" t="s"/>
-      <x:c r="D29" s="29" t="s"/>
-      <x:c r="E29" s="29" t="s"/>
-      <x:c r="F29" s="30" t="n">
+      <x:c r="B29" s="25" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="28" t="s">
+      <x:c r="B30" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C30" s="29" t="s"/>
-      <x:c r="D30" s="29" t="s"/>
-      <x:c r="E30" s="29" t="s"/>
-      <x:c r="F30" s="30" t="n">
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="28" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C31" s="29" t="s"/>
-      <x:c r="D31" s="29" t="s"/>
-      <x:c r="E31" s="29" t="s"/>
-      <x:c r="F31" s="30" t="n">
+      <x:c r="B31" s="25" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="31" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C32" s="32" t="s"/>
-      <x:c r="D32" s="32" t="s"/>
-      <x:c r="E32" s="32" t="s"/>
-      <x:c r="F32" s="33" t="n">
+      <x:c r="B32" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C32" s="29" t="s"/>
+      <x:c r="D32" s="29" t="s"/>
+      <x:c r="E32" s="29" t="s"/>
+      <x:c r="F32" s="30" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -1579,7 +1579,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1619,7 +1619,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1658,7 +1658,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1696,7 +1696,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1734,7 +1734,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -2957,7 +2957,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2997,7 +2997,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>42</x:v>
@@ -3036,7 +3036,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
@@ -3074,7 +3074,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
@@ -3112,7 +3112,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
@@ -3150,7 +3150,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3188,7 +3188,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
@@ -4442,7 +4442,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -4482,7 +4482,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="31" t="s">
         <x:v>74</x:v>
@@ -5711,7 +5711,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -5751,7 +5751,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="31" t="s">
         <x:v>74</x:v>
@@ -6980,7 +6980,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -7020,7 +7020,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>87</x:v>
@@ -7059,7 +7059,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -8284,7 +8284,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -8324,7 +8324,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>74</x:v>
@@ -8363,7 +8363,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>104</x:v>
       </x:c>
@@ -8401,7 +8401,7 @@
         <x:v>110</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -8439,7 +8439,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -8477,7 +8477,7 @@
         <x:v>110</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -9721,7 +9721,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -9761,7 +9761,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>74</x:v>
@@ -9800,7 +9800,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
@@ -9838,7 +9838,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -9876,7 +9876,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11099,7 +11099,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -11139,7 +11139,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>104</x:v>
@@ -11178,7 +11178,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11216,7 +11216,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11254,7 +11254,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11292,7 +11292,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11330,7 +11330,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11368,7 +11368,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11406,7 +11406,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11444,7 +11444,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11482,7 +11482,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11520,7 +11520,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11558,7 +11558,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -11596,7 +11596,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -11634,7 +11634,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -11672,7 +11672,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -11710,7 +11710,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -11748,7 +11748,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
         <x:v>32</x:v>
       </x:c>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="223">
   <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>MANUEL NACUA</x:t>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="223">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="215">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -37,9 +37,6 @@
     <x:t>MANUEL NACUA</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | July 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -154,9 +151,6 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | August 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -250,9 +244,6 @@
     <x:t>1215865</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | September 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -271,9 +262,6 @@
     <x:t>1215880</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | November 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>AGAPITO PERATER BERALLO</x:t>
   </x:si>
   <x:si>
@@ -289,9 +277,6 @@
     <x:t>1215998</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | December 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Amateur Radio Station License (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -325,9 +310,6 @@
     <x:t>1216037</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | January 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>MARENIE CAJETAS FLORA</x:t>
   </x:si>
   <x:si>
@@ -400,9 +382,6 @@
     <x:t>1216082</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | February 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>EMELIO LUZON PANOY</x:t>
   </x:si>
   <x:si>
@@ -455,9 +434,6 @@
   </x:si>
   <x:si>
     <x:t>1216130</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>ARTURO D ANTONIO</x:t>
@@ -1036,7 +1012,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1051,6 +1027,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1123,7 +1102,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1159,6 +1138,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1545,20 +1528,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1581,249 +1564,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45862.2568792245</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45908</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45862.2568792245</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45908</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45862.3066347569</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>45861.1595728241</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45862.3066347569</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="L9" s="19">
+        <x:v>45862.1034618403</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45861.1595728241</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45862.1034618403</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="E10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45861.1361588889</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45861.1361588889</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="K10" s="18" t="n">
+        <x:v>7950</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45862.1391293403</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45861.1810907407</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>7950</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45862.1391293403</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="J11" s="16" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45861.1810907407</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46273</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>45862.1344605671</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
+      <x:c r="B14" s="20" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -2923,20 +2906,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45870</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2959,358 +2942,358 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45866.2802922106</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45866.2803013889</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45873.1184145139</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45866.2802922106</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45866.2803013889</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="C9" s="15" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45873.1184145139</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45875.2238915046</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>4030</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>45876.2433041204</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45875.2238915046</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
+      <x:c r="C10" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>45875.3617282407</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>4030</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45876.2433041204</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="J10" s="16" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="K10" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45876.2230995023</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45875.3617282407</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="H11" s="17">
+        <x:v>45875.2324767593</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45876.2230995023</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="L11" s="19">
+        <x:v>45876.2319890162</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45875.2324767593</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>45876.2319890162</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="F12" s="15" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="G12" s="15" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="H12" s="17">
+        <x:v>45879.4885117361</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="K12" s="18" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>45884.2776561458</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45879.4885117361</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
+      <x:c r="C13" s="15" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>1650</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>45884.2776561458</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="D13" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="H13" s="17">
+        <x:v>45887.5499379745</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45887.5499545023</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45887.5499379745</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>45887.5499545023</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="19">
         <x:v>45891.1027280787</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="19" t="s">
+      <x:c r="B16" s="20" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="23" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C16" s="20" t="s"/>
-      <x:c r="D16" s="20" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="21" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="22" t="s">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="s">
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C23" s="29" t="s"/>
-      <x:c r="D23" s="29" t="s"/>
-      <x:c r="E23" s="29" t="s"/>
-      <x:c r="F23" s="30" t="n">
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4408,20 +4391,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45901</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4444,81 +4427,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="31" t="s">
+      <x:c r="B8" s="32" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C8" s="32" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="32" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F8" s="32" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C8" s="31" t="s">
+      <x:c r="G8" s="32" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="31" t="s">
+      <x:c r="H8" s="33">
+        <x:v>45887.291765787</x:v>
+      </x:c>
+      <x:c r="I8" s="33">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J8" s="32" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F8" s="31" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G8" s="31" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H8" s="32">
-        <x:v>45887.291765787</x:v>
-      </x:c>
-      <x:c r="I8" s="32">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J8" s="31" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="34" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="32">
+      <x:c r="L8" s="33">
         <x:v>45903.117765081</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="32" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -4537,44 +4520,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="19" t="s">
+      <x:c r="B11" s="20" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="s"/>
+      <x:c r="D11" s="21" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="22" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="23" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C11" s="20" t="s"/>
-      <x:c r="D11" s="20" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="21" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="22" t="s">
+      <x:c r="C12" s="24" t="s"/>
+      <x:c r="D12" s="24" t="s"/>
+      <x:c r="E12" s="24" t="s"/>
+      <x:c r="F12" s="25" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C12" s="23" t="s"/>
-      <x:c r="D12" s="23" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="24" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="26" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="25" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C13" s="26" t="s"/>
-      <x:c r="D13" s="26" t="s"/>
-      <x:c r="E13" s="26" t="s"/>
-      <x:c r="F13" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s"/>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="30" t="n">
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -5677,20 +5660,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45962</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5713,81 +5696,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="31" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C8" s="31" t="s">
+      <x:c r="B8" s="32" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C8" s="32" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="32" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F8" s="32" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G8" s="32" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H8" s="33">
+        <x:v>45944.1129354167</x:v>
+      </x:c>
+      <x:c r="I8" s="33">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J8" s="32" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="31" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F8" s="31" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G8" s="31" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H8" s="32">
-        <x:v>45944.1129354167</x:v>
-      </x:c>
-      <x:c r="I8" s="32">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J8" s="31" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="34" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="32">
+      <x:c r="L8" s="33">
         <x:v>45971.3164108796</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="32" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -5806,44 +5789,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="19" t="s">
+      <x:c r="B11" s="20" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="s"/>
+      <x:c r="D11" s="21" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="22" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="23" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C11" s="20" t="s"/>
-      <x:c r="D11" s="20" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="21" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="22" t="s">
+      <x:c r="C12" s="24" t="s"/>
+      <x:c r="D12" s="24" t="s"/>
+      <x:c r="E12" s="24" t="s"/>
+      <x:c r="F12" s="25" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C12" s="23" t="s"/>
-      <x:c r="D12" s="23" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="24" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="26" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="25" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C13" s="26" t="s"/>
-      <x:c r="D13" s="26" t="s"/>
-      <x:c r="E13" s="26" t="s"/>
-      <x:c r="F13" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s"/>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="30" t="n">
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -6946,20 +6929,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6982,173 +6965,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46000.4750792361</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46013.2950574421</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46000.4750792361</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45992</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="H9" s="17">
+        <x:v>46000.1807785301</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>744</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46013.2950574421</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46000.1807785301</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="18" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>46006.2645192361</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="21" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="22" t="s">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="s">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="26" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8250,20 +8233,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -8286,309 +8269,309 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46031.0429770602</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46015</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46043.2977226505</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46031.0429770602</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46015</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="H9" s="17">
+        <x:v>46029.1168153009</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45778</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46043.2977226505</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46036.0526802894</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46029.1168153009</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45778</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="H10" s="17">
+        <x:v>46034.1687700231</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45944</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46036.0526802894</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
+      <x:c r="K10" s="18" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46044.2632803241</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
         <x:v>110</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>46029.1129715509</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45999</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="K11" s="18" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46036.0583638426</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46034.1687700231</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="G12" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46034.174115162</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46044.2632803241</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="J12" s="16" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46029.1129715509</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45999</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46036.0583638426</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46034.174115162</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45944</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="19">
         <x:v>46044.2691750116</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="19" t="s">
+      <x:c r="B15" s="20" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="22" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="23" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="21" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="22" t="s">
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="s">
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B21" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C21" s="29" t="s"/>
-      <x:c r="D21" s="29" t="s"/>
-      <x:c r="E21" s="29" t="s"/>
-      <x:c r="F21" s="30" t="n">
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -9687,20 +9670,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9723,249 +9706,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46050.1475945255</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45988</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46057.9737815278</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>46066.1502727199</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46139</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46077.954281088</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46050.1475945255</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45988</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46057.9737815278</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>46066.1893041088</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45695</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="K10" s="18" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46076.0521240394</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46066.1502727199</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46139</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46077.954281088</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>46066.1860957755</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45695</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46066.1893041088</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45695</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46076.0521240394</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46066.1860957755</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45695</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>46076.0476356713</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
+      <x:c r="B14" s="20" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -11065,20 +11048,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -11101,754 +11084,754 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46072.3153026736</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46090.3114235417</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>46072.0333546991</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46090.2584930556</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46072.3153026736</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46114</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="G10" s="15" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46071.1677711806</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46091.1948946528</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46070.1768476389</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46084.1495253588</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46071.3305731597</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46094.1906452199</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46072.1089512963</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46090.2365117824</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46072.0792950116</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46090.220792662</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46072.0497342708</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46090.2102464352</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46071.2285509838</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46090.0772934491</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46071.2072683796</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46090.0616673032</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46079.0151889352</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>45602</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>3990</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46093.1514429977</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46073.0262962616</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46090.2670310069</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46073.0478536458</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46090.2431909954</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46073.10951125</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46090.3114235417</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46072.0333546991</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46090.2584930556</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46071.1677711806</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46091.1948946528</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46070.1768476389</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46123</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46084.1495253588</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46071.3305731597</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46094.1906452199</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46072.1089512963</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46090.2365117824</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46072.0792950116</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46090.220792662</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46072.0497342708</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46090.2102464352</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46071.2285509838</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46090.0772934491</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46071.2072683796</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46090.0616673032</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46079.0151889352</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>45602</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3990</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46093.1514429977</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
+      <x:c r="L21" s="19">
+        <x:v>46091.1210900116</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46073.0262962616</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="F22" s="15" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46073.0611031366</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46090.2670310069</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46073.0478536458</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46090.2431909954</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
+      <x:c r="L22" s="19">
+        <x:v>46090.2266513079</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="D23" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="G23" s="15" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46073.10951125</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
+      <x:c r="H23" s="17">
+        <x:v>46073.0763545833</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J21" s="15" t="s">
+      <x:c r="J23" s="16" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="K21" s="17" t="n">
+      <x:c r="K23" s="18" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46091.1210900116</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
+      <x:c r="L23" s="19">
+        <x:v>46090.2162962268</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
+      <x:c r="D24" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="s">
+      <x:c r="F24" s="15" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46073.0611031366</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46036</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
+      <x:c r="G24" s="15" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46090.2266513079</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
+      <x:c r="H24" s="17">
+        <x:v>46071.2853697569</x:v>
+      </x:c>
+      <x:c r="I24" s="17">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46073.0763545833</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
+      <x:c r="K24" s="18" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46090.2162962268</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46071.2853697569</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
+      <x:c r="L24" s="19">
         <x:v>46094.1777229282</x:v>
       </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M24" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="19" t="s">
+      <x:c r="B27" s="20" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C27" s="21" t="s"/>
+      <x:c r="D27" s="21" t="s"/>
+      <x:c r="E27" s="22" t="s"/>
+      <x:c r="F27" s="22" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="23" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C27" s="20" t="s"/>
-      <x:c r="D27" s="20" t="s"/>
-      <x:c r="E27" s="21" t="s"/>
-      <x:c r="F27" s="21" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="22" t="s">
+      <x:c r="C28" s="24" t="s"/>
+      <x:c r="D28" s="24" t="s"/>
+      <x:c r="E28" s="24" t="s"/>
+      <x:c r="F28" s="25" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C28" s="23" t="s"/>
-      <x:c r="D28" s="23" t="s"/>
-      <x:c r="E28" s="23" t="s"/>
-      <x:c r="F28" s="24" t="s">
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="26" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B32" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="25" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C29" s="26" t="s"/>
-      <x:c r="D29" s="26" t="s"/>
-      <x:c r="E29" s="26" t="s"/>
-      <x:c r="F29" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C30" s="26" t="s"/>
-      <x:c r="D30" s="26" t="s"/>
-      <x:c r="E30" s="26" t="s"/>
-      <x:c r="F30" s="27" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="25" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C31" s="26" t="s"/>
-      <x:c r="D31" s="26" t="s"/>
-      <x:c r="E31" s="26" t="s"/>
-      <x:c r="F31" s="27" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C32" s="29" t="s"/>
-      <x:c r="D32" s="29" t="s"/>
-      <x:c r="E32" s="29" t="s"/>
-      <x:c r="F32" s="30" t="n">
+      <x:c r="C32" s="30" t="s"/>
+      <x:c r="D32" s="30" t="s"/>
+      <x:c r="E32" s="30" t="s"/>
+      <x:c r="F32" s="31" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-MANUEL-NACUA-evaluator-cache-serviceTracking-MANUEL-NACUA-IX-202501-202612.xlsx
@@ -685,7 +685,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -725,14 +725,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1012,7 +1004,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1023,16 +1015,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1044,65 +1033,65 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1137,99 +1126,95 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1531,17 +1516,17 @@
       <x:c r="B5" s="12">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1564,249 +1549,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45862.2568792245</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45908</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45862.3066347569</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45861.1595728241</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46238</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45862.1034618403</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45861.1361588889</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>7950</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45862.1391293403</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45861.1810907407</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45862.1344605671</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -2909,17 +2894,17 @@
       <x:c r="B5" s="12">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2942,358 +2927,358 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45866.2802922106</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45866.2803013889</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45873.1184145139</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45875.2238915046</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>4030</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45876.2433041204</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45875.3617282407</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45876.2230995023</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45875.2324767593</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45876.2319890162</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45879.4885117361</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45888</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1650</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45884.2776561458</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45887.5499379745</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45887.5499545023</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45891.1027280787</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+      <x:c r="B16" s="19" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
+      <x:c r="B19" s="25" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="29" t="s">
+      <x:c r="B23" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
+      <x:c r="C23" s="29" t="s"/>
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="29" t="s"/>
+      <x:c r="F23" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4394,17 +4379,17 @@
       <x:c r="B5" s="12">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4427,80 +4412,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="32" t="s">
+      <x:c r="B8" s="31" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="s">
+      <x:c r="C8" s="31" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D8" s="32" t="s">
+      <x:c r="D8" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="32" t="s">
+      <x:c r="E8" s="31" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="F8" s="32" t="s">
+      <x:c r="F8" s="31" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G8" s="32" t="s">
+      <x:c r="G8" s="31" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="H8" s="33">
+      <x:c r="H8" s="32">
         <x:v>45887.291765787</x:v>
       </x:c>
-      <x:c r="I8" s="33">
+      <x:c r="I8" s="32">
         <x:v>45883</x:v>
       </x:c>
-      <x:c r="J8" s="32" t="s">
+      <x:c r="J8" s="31" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="K8" s="34" t="n">
+      <x:c r="K8" s="33" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="33">
+      <x:c r="L8" s="32">
         <x:v>45903.117765081</x:v>
       </x:c>
-      <x:c r="M8" s="32" t="s">
+      <x:c r="M8" s="31" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -4520,44 +4505,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="20" t="s">
+      <x:c r="B11" s="19" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="22" t="s"/>
+      <x:c r="C11" s="20" t="s"/>
+      <x:c r="D11" s="20" t="s"/>
+      <x:c r="E11" s="21" t="s"/>
+      <x:c r="F11" s="21" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="23" t="s">
+      <x:c r="B12" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="s">
+      <x:c r="C12" s="23" t="s"/>
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="24" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
+      <x:c r="B13" s="25" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+      <x:c r="B14" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -5663,17 +5648,17 @@
       <x:c r="B5" s="12">
         <x:v>45962</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5696,80 +5681,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="32" t="s">
+      <x:c r="B8" s="31" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="s">
+      <x:c r="C8" s="31" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D8" s="32" t="s">
+      <x:c r="D8" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="32" t="s">
+      <x:c r="E8" s="31" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F8" s="32" t="s">
+      <x:c r="F8" s="31" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G8" s="32" t="s">
+      <x:c r="G8" s="31" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H8" s="33">
+      <x:c r="H8" s="32">
         <x:v>45944.1129354167</x:v>
       </x:c>
-      <x:c r="I8" s="33">
+      <x:c r="I8" s="32">
         <x:v>45920</x:v>
       </x:c>
-      <x:c r="J8" s="32" t="s">
+      <x:c r="J8" s="31" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="K8" s="34" t="n">
+      <x:c r="K8" s="33" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="33">
+      <x:c r="L8" s="32">
         <x:v>45971.3164108796</x:v>
       </x:c>
-      <x:c r="M8" s="32" t="s">
+      <x:c r="M8" s="31" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -5789,44 +5774,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="20" t="s">
+      <x:c r="B11" s="19" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="22" t="s"/>
+      <x:c r="C11" s="20" t="s"/>
+      <x:c r="D11" s="20" t="s"/>
+      <x:c r="E11" s="21" t="s"/>
+      <x:c r="F11" s="21" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="23" t="s">
+      <x:c r="B12" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="s">
+      <x:c r="C12" s="23" t="s"/>
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="24" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
+      <x:c r="B13" s="25" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+      <x:c r="B14" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -6932,17 +6917,17 @@
       <x:c r="B5" s="12">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6965,173 +6950,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46000.4750792361</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>744</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46013.2950574421</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46000.1807785301</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46006.2645192361</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8236,17 +8221,17 @@
       <x:c r="B5" s="12">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -8269,309 +8254,309 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46031.0429770602</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46015</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46043.2977226505</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46029.1168153009</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45778</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46036.0526802894</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46034.1687700231</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46044.2632803241</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46029.1129715509</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45999</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46036.0583638426</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46034.174115162</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46044.2691750116</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="20" t="s">
+      <x:c r="B15" s="19" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="22" t="s"/>
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="21" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="s">
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
+      <x:c r="B19" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="29" t="s">
+      <x:c r="B21" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
+      <x:c r="C21" s="29" t="s"/>
+      <x:c r="D21" s="29" t="s"/>
+      <x:c r="E21" s="29" t="s"/>
+      <x:c r="F21" s="30" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -9673,17 +9658,17 @@
       <x:c r="B5" s="12">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9706,249 +9691,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46050.1475945255</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45988</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46057.9737815278</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46066.1502727199</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46139</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46077.954281088</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46066.1893041088</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46076.0521240394</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46066.1860957755</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46076.0476356713</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -11051,17 +11036,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -11084,754 +11069,754 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46072.3153026736</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46114</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46090.3114235417</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46072.0333546991</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46090.2584930556</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46071.1677711806</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46091.1948946528</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46070.1768476389</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46084.1495253588</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46071.3305731597</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46094.1906452199</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46072.1089512963</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46090.2365117824</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46072.0792950116</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46090.220792662</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46072.0497342708</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46090.2102464352</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46071.2285509838</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46090.0772934491</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46071.2072683796</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46090.0616673032</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>46079.0151889352</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>45602</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>46093.1514429977</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>46073.0262962616</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>46090.2670310069</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>46073.0478536458</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>46090.2431909954</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="14" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="16">
         <x:v>46073.10951125</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="16">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="18">
         <x:v>46091.1210900116</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="14" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s">
+      <x:c r="D22" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E22" s="14" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="14" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="16">
         <x:v>46073.0611031366</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="16">
         <x:v>46036</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="s">
+      <x:c r="J22" s="15" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="18">
         <x:v>46090.2266513079</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="15" t="s">
+      <x:c r="B23" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="s">
+      <x:c r="C23" s="14" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="s">
+      <x:c r="D23" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="s">
+      <x:c r="E23" s="14" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="s">
+      <x:c r="F23" s="14" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="G23" s="15" t="s">
+      <x:c r="G23" s="14" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="H23" s="17">
+      <x:c r="H23" s="16">
         <x:v>46073.0763545833</x:v>
       </x:c>
-      <x:c r="I23" s="17">
+      <x:c r="I23" s="16">
         <x:v>45824</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="s">
+      <x:c r="J23" s="15" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="K23" s="18" t="n">
+      <x:c r="K23" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L23" s="19">
+      <x:c r="L23" s="18">
         <x:v>46090.2162962268</x:v>
       </x:c>
-      <x:c r="M23" s="15" t="s">
+      <x:c r="M23" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="15" t="s">
+      <x:c r="B24" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="s">
+      <x:c r="C24" s="14" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="s">
+      <x:c r="D24" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="s">
+      <x:c r="E24" s="14" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="s">
+      <x:c r="F24" s="14" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="G24" s="15" t="s">
+      <x:c r="G24" s="14" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="H24" s="17">
+      <x:c r="H24" s="16">
         <x:v>46071.2853697569</x:v>
       </x:c>
-      <x:c r="I24" s="17">
+      <x:c r="I24" s="16">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="s">
+      <x:c r="J24" s="15" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="K24" s="18" t="n">
+      <x:c r="K24" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L24" s="19">
+      <x:c r="L24" s="18">
         <x:v>46094.1777229282</x:v>
       </x:c>
-      <x:c r="M24" s="15" t="s">
+      <x:c r="M24" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="20" t="s">
+      <x:c r="B27" s="19" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C27" s="21" t="s"/>
-      <x:c r="D27" s="21" t="s"/>
-      <x:c r="E27" s="22" t="s"/>
-      <x:c r="F27" s="22" t="s"/>
+      <x:c r="C27" s="20" t="s"/>
+      <x:c r="D27" s="20" t="s"/>
+      <x:c r="E27" s="21" t="s"/>
+      <x:c r="F27" s="21" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="23" t="s">
+      <x:c r="B28" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C28" s="24" t="s"/>
-      <x:c r="D28" s="24" t="s"/>
-      <x:c r="E28" s="24" t="s"/>
-      <x:c r="F28" s="25" t="s">
+      <x:c r="C28" s="23" t="s"/>
+      <x:c r="D28" s="23" t="s"/>
+      <x:c r="E28" s="23" t="s"/>
+      <x:c r="F28" s="24" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
+      <x:c r="B29" s="25" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
+      <x:c r="B30" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
+      <x:c r="B31" s="25" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="29" t="s">
+      <x:c r="B32" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C32" s="30" t="s"/>
-      <x:c r="D32" s="30" t="s"/>
-      <x:c r="E32" s="30" t="s"/>
-      <x:c r="F32" s="31" t="n">
+      <x:c r="C32" s="29" t="s"/>
+      <x:c r="D32" s="29" t="s"/>
+      <x:c r="E32" s="29" t="s"/>
+      <x:c r="F32" s="30" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
